--- a/naver-place-crawler/results_nail/서구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서구_네일샵.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="n">
         <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4553,13 +4553,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Q44" t="n">
         <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5391,13 +5391,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q53" t="n">
         <v>218</v>
       </c>
       <c r="R53" t="n">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5676,10 +5676,10 @@
         <v>130</v>
       </c>
       <c r="Q56" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R56" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>608</v>
       </c>
       <c r="Q67" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R67" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/서구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서구_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일무우 인천검단점</t>
+          <t>제이언니네 청라본점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>n_mou@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1382-9824</t>
+          <t>0507-1332-6316</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/n_mou</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>326</v>
+        <v>663</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="R2" t="n">
-        <v>340</v>
+        <v>830</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1965956470</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965956470</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1248네일</t>
+          <t>프롬쥬네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1248nail@naver.com</t>
+          <t>dlaalswn89@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1479-8978</t>
+          <t>0507-1327-0666</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1248_nail</t>
+          <t>https://blog.naver.com/dlaalswn89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>448</v>
+        <v>570</v>
       </c>
       <c r="Q3" t="n">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="R3" t="n">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1537239618</t>
+          <t>1545913000</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537239618</t>
+          <t>https://m.place.naver.com/place/1545913000</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일다름 인천검단점</t>
+          <t>미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>naildareum_@naver.com</t>
+          <t>mielnailbrow@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1431-4140</t>
+          <t>0507-1355-4026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 20 연세프라자 8차 309호</t>
+          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_CIgvC</t>
+          <t>https://www.instagram.com/mielnailbrow_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>419</v>
+        <v>730</v>
       </c>
       <c r="Q4" t="n">
-        <v>102</v>
+        <v>397</v>
       </c>
       <c r="R4" t="n">
-        <v>521</v>
+        <v>1127</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1735874545</t>
+          <t>409746804</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735874545</t>
+          <t>https://m.place.naver.com/place/409746804</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일디핀</t>
+          <t>네일으니크</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ria_world@naver.com</t>
+          <t>rohyunji8442@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1476-4029</t>
+          <t>0507-1394-1471</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildeepin</t>
+          <t>https://pf.kakao.com/_xjfJWG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>75</v>
+        <v>429</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="R5" t="n">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2047454568</t>
+          <t>1466509562</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047454568</t>
+          <t>https://m.place.naver.com/place/1466509562</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오오샵 검단점</t>
+          <t>뷰티드시엘</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dhaldud10@naver.com</t>
+          <t>jysjysyessle@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>070-4062-0556</t>
+          <t>0507-1448-4452</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 159 1층 105호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop/</t>
+          <t>https://www.instagram.com/beauty_du_ciel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>606</v>
+        <v>173</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="R6" t="n">
-        <v>631</v>
+        <v>253</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1739642099</t>
+          <t>1538853353</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739642099</t>
+          <t>https://m.place.naver.com/place/1538853353</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
+          <t>레푸스 청라점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dodofamily_mam@naver.com</t>
+          <t>dldeoqkr@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1337-0812</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>396</v>
+        <v>296</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="R7" t="n">
-        <v>436</v>
+        <v>364</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1742485791</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1742485791</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MeYou Nail 미유네일</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>myeongmy1012@naver.com</t>
+          <t>mobi04@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>070-7576-3091</t>
+          <t>0507-1398-8291</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 31-1</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meyou__nail</t>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>52</v>
+        <v>573</v>
       </c>
       <c r="Q8" t="n">
-        <v>82</v>
+        <v>834</v>
       </c>
       <c r="R8" t="n">
-        <v>134</v>
+        <v>1407</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1831252046</t>
+          <t>1090442730</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1831252046</t>
+          <t>https://m.place.naver.com/place/1090442730</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31네일스튜디오</t>
+          <t>네일도속눈썹</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>naildorash1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1384-3385</t>
+          <t>0507-1395-6008</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로685번길 31 2층</t>
+          <t>인천광역시 서구 염곡로 346-1 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rxmAFK</t>
+          <t>http://instagram.com/naildo_lash</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>590</v>
+        <v>404</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="R9" t="n">
-        <v>614</v>
+        <v>693</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1533854785</t>
+          <t>1958392738</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533854785</t>
+          <t>https://m.place.naver.com/place/1958392738</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>네일벨</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mobi04@naver.com</t>
+          <t>nailbelle@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1398-8291</t>
+          <t>0507-1324-7499</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 원창로229번길 39 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>http://pf.kakao.com/_Nmwmxb</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>575</v>
+        <v>138</v>
       </c>
       <c r="Q10" t="n">
-        <v>824</v>
+        <v>215</v>
       </c>
       <c r="R10" t="n">
-        <v>1399</v>
+        <v>353</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>1895861710</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/1895861710</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인생네일 청라본점</t>
+          <t>에스영이네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>askflclsrna@naver.com</t>
+          <t>s02nail@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1301-5228</t>
+          <t>0507-1322-9488</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/life_nail_salon</t>
+          <t>http://pf.kakao.com/_JAxdFs</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1458,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>345</v>
+        <v>426</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>188</v>
       </c>
       <c r="R11" t="n">
-        <v>356</v>
+        <v>614</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1764464663</t>
+          <t>1726483094</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764464663</t>
+          <t>https://m.place.naver.com/place/1726483094</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1504,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>와우뷰티 청라점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>e5174@naver.com</t>
-        </is>
-      </c>
+          <t>루미온네일 검단신도시점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1323-1043</t>
+          <t>0507-1347-5944</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1561,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1012993987</t>
+          <t>2012993603</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012993987</t>
+          <t>https://m.place.naver.com/place/2012993603</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>레푸스검단점&amp;로브</t>
+          <t>루비네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>refussgumdan@naver.com</t>
+          <t>ruby1004_mj@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1345-7844</t>
+          <t>0507-1486-3019</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
+          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_gumdan</t>
+          <t>https://www.instagram.com/rubynail3006</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1655,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>503</v>
+        <v>279</v>
       </c>
       <c r="Q13" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="R13" t="n">
-        <v>653</v>
+        <v>339</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1967477084</t>
+          <t>1233475580</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967477084</t>
+          <t>https://m.place.naver.com/place/1233475580</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1692,34 +1688,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에스영이네일</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>s02nail@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1322-9488</t>
+          <t>0507-1344-1735</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JAxdFs</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1740,7 +1736,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1749,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>425</v>
+        <v>258</v>
       </c>
       <c r="Q14" t="n">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="R14" t="n">
-        <v>613</v>
+        <v>287</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1726483094</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726483094</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1786,34 +1782,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일으니크</t>
+          <t>네일글로우</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>yulee410@naver.com</t>
+          <t>cottonpp@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1394-1471</t>
+          <t>0507-1460-8342</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
+          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjfJWG</t>
+          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1834,7 +1830,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1843,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>428</v>
+        <v>63</v>
       </c>
       <c r="Q15" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="R15" t="n">
-        <v>515</v>
+        <v>120</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1466509562</t>
+          <t>2075971036</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466509562</t>
+          <t>https://m.place.naver.com/place/2075971036</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1880,34 +1876,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
+          <t>섬세하나네일 청라본점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dbdlzkzn123@naver.com</t>
+          <t>sumsehana@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1481-0788</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>https://blog.naver.com/sumsehana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1917,7 +1913,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1928,7 +1924,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1937,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>337</v>
+        <v>615</v>
       </c>
       <c r="Q16" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="R16" t="n">
-        <v>412</v>
+        <v>746</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>1251340543</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/1251340543</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1974,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>어반네일</t>
+          <t>네일을기억해</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>urban_505@naver.com</t>
+          <t>rimo0904@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1448-5118</t>
+          <t>0507-1491-7279</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 402호</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/urban_lovely_life</t>
+          <t>https://www.instagram.com/remember._nails</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2022,7 +2018,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2031,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>367</v>
+        <v>210</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="R17" t="n">
-        <v>383</v>
+        <v>254</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1069444022</t>
+          <t>1811328950</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069444022</t>
+          <t>https://m.place.naver.com/place/1811328950</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2068,34 +2064,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일은</t>
+          <t>신스티니네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>jin70826@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1356-4122</t>
+          <t>0507-1399-4665</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 232호</t>
+          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naileun_85</t>
+          <t>http://pf.kakao.com/_tkuSxj</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2116,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2125,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>191</v>
+        <v>1138</v>
       </c>
       <c r="Q18" t="n">
-        <v>228</v>
+        <v>843</v>
       </c>
       <c r="R18" t="n">
-        <v>419</v>
+        <v>1981</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1380582584</t>
+          <t>1503407402</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1380582584</t>
+          <t>https://m.place.naver.com/place/1503407402</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2162,34 +2158,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>쏭앤뷰티</t>
+          <t>라라뷰티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yuri9043@naver.com</t>
+          <t>rmatnr0203@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1398-4171</t>
+          <t>0507-1446-6698</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 8 309호</t>
+          <t>인천광역시 서구 승학로 481 301호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zxceHn</t>
+          <t>https://www.instagram.com/__lalabeauty__</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2210,7 +2206,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2219,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>42</v>
+        <v>632</v>
       </c>
       <c r="Q19" t="n">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>160</v>
+        <v>671</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2071832026</t>
+          <t>1220420271</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071832026</t>
+          <t>https://m.place.naver.com/place/1220420271</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2256,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일도속눈썹</t>
+          <t>네일달다 청라점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>naildorash1@naver.com</t>
+          <t>haru_log_in@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1395-6008</t>
+          <t>0507-1325-3255</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로 346-1 1층</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildo_lash</t>
+          <t>http://instagram.com/naildalda_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2304,7 +2300,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2313,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>403</v>
+        <v>622</v>
       </c>
       <c r="Q20" t="n">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="R20" t="n">
-        <v>692</v>
+        <v>860</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1958392738</t>
+          <t>1040857451</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958392738</t>
+          <t>https://m.place.naver.com/place/1040857451</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2350,29 +2346,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>하프네일</t>
+          <t>네일드벨라 인천검단점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>half7571@naver.com</t>
+          <t>naildebella@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1380-7571</t>
+          <t>0507-1356-3442</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
+          <t>인천광역시 서구 이음대로 384 307호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/half_nail</t>
+          <t>https://blog.naver.com/naildebella</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2387,7 +2383,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2407,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1605</v>
+        <v>263</v>
       </c>
       <c r="Q21" t="n">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="R21" t="n">
-        <v>1796</v>
+        <v>299</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2422,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1259862588</t>
+          <t>1219318994</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259862588</t>
+          <t>https://m.place.naver.com/place/1219318994</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2444,34 +2440,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>신스티니네일</t>
+          <t>네일델루나</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>johyen_@naver.com</t>
+          <t>eatingzzz@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1399-4665</t>
+          <t>0507-1358-7017</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_tkuSxj</t>
+          <t>http://instagram.com/nail_delluna</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2492,7 +2488,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2501,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1132</v>
+        <v>1523</v>
       </c>
       <c r="Q22" t="n">
-        <v>835</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
-        <v>1967</v>
+        <v>1538</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2516,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1503407402</t>
+          <t>1852644091</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503407402</t>
+          <t>https://m.place.naver.com/place/1852644091</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2538,29 +2534,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>온다네일룸</t>
+          <t>아이퀸네일 청라점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dl7246@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1369-7246</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 179 3층</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onda_nail_room/</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2595,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>732</v>
+        <v>314</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="R23" t="n">
-        <v>777</v>
+        <v>550</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2610,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1656364709</t>
+          <t>1330577008</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656364709</t>
+          <t>https://m.place.naver.com/place/1330577008</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2632,29 +2628,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>맑은네일&amp;오로지푸스 인천검단신도시점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>ekal5027@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1346-5358</t>
+          <t>0507-1318-8700</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+          <t>인천광역시 서구 서로3로 50 모아미래도 엘리트파크 상가1동109호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.grimmy</t>
+          <t>https://www.instagram.com/malgunnail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2689,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>349</v>
+        <v>416</v>
       </c>
       <c r="Q24" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R24" t="n">
-        <v>403</v>
+        <v>473</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2704,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1125220368</t>
+          <t>1926633328</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125220368</t>
+          <t>https://m.place.naver.com/place/1926633328</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2726,29 +2722,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>루미온네일 검단신도시점</t>
+          <t>네일또온나 청라점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yeonju9970@naver.com</t>
+          <t>2xmania2xj@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1347-5944</t>
+          <t>0507-1338-3150</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
+          <t>https://www.instagram.com/nail_tto_onna</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2783,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>27</v>
+        <v>247</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="R25" t="n">
-        <v>34</v>
+        <v>310</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2798,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2012993603</t>
+          <t>1546215593</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012993603</t>
+          <t>https://m.place.naver.com/place/1546215593</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2820,29 +2816,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>단감네일</t>
+          <t>와우뷰티 청라점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>aayoon7@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1374-8432</t>
+          <t>0507-1323-1043</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dangam_nail/</t>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2877,13 +2873,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>202</v>
+        <v>91</v>
       </c>
       <c r="Q26" t="n">
-        <v>337</v>
+        <v>48</v>
       </c>
       <c r="R26" t="n">
-        <v>539</v>
+        <v>139</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2892,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1985862694</t>
+          <t>1012993987</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985862694</t>
+          <t>https://m.place.naver.com/place/1012993987</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2914,34 +2910,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>이루아네일</t>
+          <t>네일무우 인천검단점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>woo_vely_@naver.com</t>
+          <t>n_mou@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1382-9824</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>https://blog.naver.com/n_mou</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2951,7 +2947,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2971,13 +2967,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>132</v>
+        <v>326</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>155</v>
+        <v>340</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2986,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1965956470</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1965956470</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3008,30 +3004,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일인유</t>
+          <t>이루아네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bonheur0118@naver.com</t>
+          <t>nec1153@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1400-0973</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inyou</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3061,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1177</v>
+        <v>135</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1192</v>
+        <v>158</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1117254073</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117254073</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3098,29 +3098,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>감성네일</t>
+          <t>네일바연</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gamseongnail@naver.com</t>
+          <t>yeerina@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1424-4545</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>http://instagram.com/nail.by.yeon</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3155,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>446</v>
+        <v>685</v>
       </c>
       <c r="Q29" t="n">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="R29" t="n">
-        <v>611</v>
+        <v>710</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,17 +3166,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>1017865788</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/1017865788</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3192,29 +3188,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>라나뷰티 청라본점</t>
+          <t>네일하고가람</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>dkfzhdspdlf@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1392-1325</t>
+          <t>0507-1468-0177</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_rananail</t>
+          <t>https://www.instagram.com/nailharam_</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3240,7 +3236,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3249,13 +3245,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
-        <v>481</v>
+        <v>126</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,17 +3260,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1071013615</t>
+          <t>1958882228</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071013615</t>
+          <t>https://m.place.naver.com/place/1958882228</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3286,35 +3282,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>달미네일</t>
+          <t>네일하롱</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jinjoo8570@naver.com</t>
+          <t>mimmmm95_@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1438-1442</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/aWKRY9YJt</t>
+          <t>https://www.instagram.com/nail._.harong</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>188</v>
+        <v>534</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="R31" t="n">
-        <v>197</v>
+        <v>570</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,17 +3354,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2000818117</t>
+          <t>1264211104</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000818117</t>
+          <t>https://m.place.naver.com/place/1264211104</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3376,34 +3376,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>블링뷰네일</t>
+          <t>네일인유</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bv_nail@naver.com</t>
+          <t>bonheur0118@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1350-9502</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RqUxcG</t>
+          <t>https://www.instagram.com/nail_inyou</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3424,7 +3420,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3433,13 +3429,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>115</v>
+        <v>1182</v>
       </c>
       <c r="Q32" t="n">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="R32" t="n">
-        <v>234</v>
+        <v>1197</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,17 +3444,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1259415075</t>
+          <t>1117254073</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259415075</t>
+          <t>https://m.place.naver.com/place/1117254073</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3470,29 +3466,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
+          <t>하프네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dksdidwhdk@naver.com</t>
+          <t>half7571@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1332-6316</t>
+          <t>0507-1380-7571</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>https://www.instagram.com/half_nail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3527,13 +3523,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>658</v>
+        <v>1610</v>
       </c>
       <c r="Q33" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="R33" t="n">
-        <v>824</v>
+        <v>1801</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,17 +3538,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>1259862588</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/1259862588</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3564,29 +3560,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>레푸스 청라점</t>
+          <t>카밀라네일 검단신도시점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dldeoqkr@naver.com</t>
+          <t>ojolfkj@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1337-0812</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYKKOFJe</t>
+          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3612,7 +3604,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3621,13 +3613,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>290</v>
+        <v>758</v>
       </c>
       <c r="Q34" t="n">
-        <v>68</v>
+        <v>358</v>
       </c>
       <c r="R34" t="n">
-        <v>358</v>
+        <v>1116</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,17 +3628,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1742485791</t>
+          <t>1490697723</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742485791</t>
+          <t>https://m.place.naver.com/place/1490697723</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3658,29 +3650,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>뉴아네일</t>
+          <t>네일디핀</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>zxas096@naver.com</t>
+          <t>sina1310@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1336-2796</t>
+          <t>0507-1476-4029</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 418 101호</t>
+          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newa_nail25</t>
+          <t>https://www.instagram.com/naildeepin</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3715,13 +3707,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="Q35" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="R35" t="n">
-        <v>199</v>
+        <v>91</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,17 +3722,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1799034051</t>
+          <t>2047454568</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799034051</t>
+          <t>https://m.place.naver.com/place/2047454568</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3752,29 +3744,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>루비네일</t>
+          <t>손끝한올네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ruby1004_mj@naver.com</t>
+          <t>ouo6973@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1486-3019</t>
+          <t>0507-1392-5639</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
+          <t>인천광역시 서구 바리미로 17 2층 203호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rubynail3006</t>
+          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3809,13 +3801,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="Q36" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="R36" t="n">
-        <v>339</v>
+        <v>93</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,17 +3816,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1233475580</t>
+          <t>2013624857</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233475580</t>
+          <t>https://m.place.naver.com/place/2013624857</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3846,29 +3838,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3883,7 +3875,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3903,13 +3895,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>569</v>
+        <v>212</v>
       </c>
       <c r="Q37" t="n">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="R37" t="n">
-        <v>702</v>
+        <v>220</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3918,17 +3910,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3940,25 +3932,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>라벨르뷰티</t>
+          <t>포네하네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>labelle0322@naver.com</t>
+          <t>forestnh@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1400-8523</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la__belle_beauty</t>
+          <t>https://blog.naver.com/forestnh</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3973,7 +3969,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3993,13 +3989,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1109</v>
+        <v>330</v>
       </c>
       <c r="Q38" t="n">
-        <v>249</v>
+        <v>116</v>
       </c>
       <c r="R38" t="n">
-        <v>1358</v>
+        <v>446</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4004,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1968058232</t>
+          <t>1672609930</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968058232</t>
+          <t>https://m.place.naver.com/place/1672609930</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4030,39 +4026,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일도빛나</t>
+          <t>도르네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sjh888347@naver.com</t>
+          <t>bnm4818@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1302-9518</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 551 동곡프라자 1층 107호</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_bitna</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4087,13 +4079,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>478</v>
+        <v>719</v>
       </c>
       <c r="Q39" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="R39" t="n">
-        <v>573</v>
+        <v>772</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4094,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1239607974</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239607974</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4124,34 +4116,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일소소</t>
+          <t>네일에딧</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rkswlwoddl84@naver.com</t>
+          <t>byddooroo@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1415-2417</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_so_so</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4172,7 +4160,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4181,13 +4169,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>269</v>
+        <v>778</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="R40" t="n">
-        <v>289</v>
+        <v>784</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4184,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1394957062</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394957062</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4218,29 +4206,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일하고가람</t>
+          <t>네일무디크</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>fromantic@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1468-0177</t>
+          <t>0507-1375-3428</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailharam_</t>
+          <t>https://www.instagram.com/nail_moodique</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4275,13 +4263,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R41" t="n">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4278,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1958882228</t>
+          <t>1811715033</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958882228</t>
+          <t>https://m.place.naver.com/place/1811715033</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4312,29 +4300,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일희 검단신도시점</t>
+          <t>라나뷰티 청라본점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>gosm06@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1398-9916</t>
+          <t>0507-1392-1325</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailhee_</t>
+          <t>https://www.instagram.com/_rananail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4360,7 +4348,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4369,13 +4357,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>340</v>
+        <v>459</v>
       </c>
       <c r="Q42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
-        <v>355</v>
+        <v>484</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4372,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1280546741</t>
+          <t>1071013615</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280546741</t>
+          <t>https://m.place.naver.com/place/1071013615</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4406,34 +4394,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>네일갱 인천검단점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>haery_kim@naver.com</t>
+          <t>nailgang_@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1309-5041</t>
+          <t>0507-1353-4100</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+          <t>http://pf.kakao.com/_bJxdCG</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4454,7 +4442,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4463,13 +4451,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>212</v>
+        <v>1695</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="R43" t="n">
-        <v>220</v>
+        <v>1726</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,17 +4466,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1024146721</t>
+          <t>1098311831</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024146721</t>
+          <t>https://m.place.naver.com/place/1098311831</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4500,25 +4488,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>소요뷰티</t>
+          <t>아트스타일네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>raindrop3113@naver.com</t>
+          <t>gotitkorea@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1418-1574</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
+          <t>인천광역시 서구 염곡로464번길 30 416호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soyo._.beauty</t>
+          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4553,13 +4545,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>563</v>
+        <v>116</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>289</v>
       </c>
       <c r="R44" t="n">
-        <v>568</v>
+        <v>405</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,17 +4560,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1142806255</t>
+          <t>1976908458</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142806255</t>
+          <t>https://m.place.naver.com/place/1976908458</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4590,29 +4582,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뷰티드시엘</t>
+          <t>오늘도네일도</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jysjysyessle@naver.com</t>
+          <t>nail_oneul@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1448-4452</t>
+          <t>0507-1449-7506</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_du_ciel</t>
+          <t>https://blog.naver.com/nail_oneul</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4627,7 +4619,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4647,13 +4639,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>173</v>
+        <v>812</v>
       </c>
       <c r="Q45" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="R45" t="n">
-        <v>253</v>
+        <v>854</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,17 +4654,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1538853353</t>
+          <t>1810678383</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538853353</t>
+          <t>https://m.place.naver.com/place/1810678383</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4684,34 +4676,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일앤젤 검단점</t>
+          <t>인생네일 청라본점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>wendy_1372@naver.com</t>
+          <t>askflclsrna@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1399-4110</t>
+          <t>0507-1301-5228</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 172 서주빌딩 503호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaxoQVn</t>
+          <t>https://www.instagram.com/life_nail_salon</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4732,22 +4724,22 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>74</v>
+        <v>350</v>
       </c>
       <c r="Q46" t="n">
-        <v>356</v>
+        <v>11</v>
       </c>
       <c r="R46" t="n">
-        <v>430</v>
+        <v>361</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,17 +4748,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1179815530</t>
+          <t>1764464663</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179815530</t>
+          <t>https://m.place.naver.com/place/1764464663</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4778,25 +4770,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>젤로미네일</t>
+          <t>무드온네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>nailjellomi@naver.com</t>
+          <t>llggggll@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1494-6716</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 3층 305호</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.jellomi</t>
+          <t>https://www.instagram.com/moodon.nail</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4831,13 +4827,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="Q47" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="R47" t="n">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,17 +4842,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2051638884</t>
+          <t>2044601280</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051638884</t>
+          <t>https://m.place.naver.com/place/2044601280</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4868,34 +4864,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일글로우</t>
+          <t>오늘의기분 네일 청라본점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>cottonpp@naver.com</t>
+          <t>bae_tamine@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1460-8342</t>
+          <t>0507-1307-8929</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_pxcsgb</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4916,7 +4912,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4925,13 +4921,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>63</v>
+        <v>347</v>
       </c>
       <c r="Q48" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="R48" t="n">
-        <v>120</v>
+        <v>424</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,17 +4936,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2075971036</t>
+          <t>1747055394</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075971036</t>
+          <t>https://m.place.naver.com/place/1747055394</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4962,35 +4958,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>도르네일</t>
+          <t>뉴아네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>s_e_y_0615@naver.com</t>
+          <t>wlsdl2102@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1336-2796</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+          <t>인천광역시 서구 승학로 418 101호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/hCmFKNexK</t>
+          <t>https://www.instagram.com/newa_nail25</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>689</v>
+        <v>88</v>
       </c>
       <c r="Q49" t="n">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="R49" t="n">
-        <v>733</v>
+        <v>212</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5030,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1001824596</t>
+          <t>1799034051</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001824596</t>
+          <t>https://m.place.naver.com/place/1799034051</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5052,29 +5052,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일드화</t>
+          <t>제이제이네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>wnghk0000@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1401-4929</t>
+          <t>0507-1319-1270</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 70 3층 303호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailedhwa?igsh=MWRnNDcweHFicGNyYg==</t>
+          <t>https://www.instagram.com/jj__nail___</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5109,13 +5109,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5124,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1657434019</t>
+          <t>2011413114</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657434019</t>
+          <t>https://m.place.naver.com/place/2011413114</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5146,29 +5146,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>가비앤네일</t>
+          <t>이르미네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jmoh95@naver.com</t>
+          <t>aboutdanchuu@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1351-4914</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 100 1층 가비앤네일</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XKZexj</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5203,13 +5203,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="R51" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5218,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1145821785</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145821785</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5240,34 +5240,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>이르미네일</t>
+          <t>오오샵 가좌점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>aboutdanchuu@naver.com</t>
+          <t>dodofamily_mam@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1391-3129</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ezxgrG</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5288,7 +5288,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5297,13 +5297,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>234</v>
+        <v>406</v>
       </c>
       <c r="Q52" t="n">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="R52" t="n">
-        <v>341</v>
+        <v>446</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5312,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1596414337</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596414337</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5334,29 +5334,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
+          <t>단감네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dlgufl0924@naver.com</t>
+          <t>aayoon7@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1408-0807</t>
+          <t>0507-1374-8432</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lantienail_official/</t>
+          <t>https://www.instagram.com/dangam_nail/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5391,13 +5391,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>610</v>
+        <v>205</v>
       </c>
       <c r="Q53" t="n">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="R53" t="n">
-        <v>828</v>
+        <v>542</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5406,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>37922472</t>
+          <t>1985862694</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37922472</t>
+          <t>https://m.place.naver.com/place/1985862694</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5428,29 +5428,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>소요뷰티</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>raindrop3113@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1481-0788</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://www.instagram.com/soyo._.beauty</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5465,7 +5461,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5485,13 +5481,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>603</v>
+        <v>573</v>
       </c>
       <c r="Q54" t="n">
-        <v>128</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>731</v>
+        <v>578</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5496,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1142806255</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1142806255</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5522,29 +5518,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>미엘네일브로우 인천가정점</t>
+          <t>네일,사계절</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mielnailbrow@naver.com</t>
+          <t>siryyam@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1355-4026</t>
+          <t>0507-1360-4822</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
+          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mielnailbrow_</t>
+          <t>https://www.instagram.com/nail_4season</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5579,13 +5575,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>727</v>
+        <v>369</v>
       </c>
       <c r="Q55" t="n">
-        <v>383</v>
+        <v>8</v>
       </c>
       <c r="R55" t="n">
-        <v>1110</v>
+        <v>377</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,17 +5590,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>409746804</t>
+          <t>1216076936</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/409746804</t>
+          <t>https://m.place.naver.com/place/1216076936</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5616,29 +5612,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>바리에라네일</t>
+          <t>해온네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mickyiii@naver.com</t>
+          <t>cocory_snb@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1390-9307</t>
+          <t>0507-1368-2279</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 8 409호</t>
+          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/varier_la_nail</t>
+          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5669,17 +5665,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="R56" t="n">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,17 +5684,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2090298265</t>
+          <t>2095874863</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090298265</t>
+          <t>https://m.place.naver.com/place/2095874863</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5710,29 +5706,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일하롱</t>
+          <t>소담뷰티 검단신도시점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mimmmm95_@naver.com</t>
+          <t>on323652@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1438-1442</t>
+          <t>0507-1484-9220</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.harong</t>
+          <t>https://www.instagram.com/sodam_beauty1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5767,13 +5763,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>531</v>
+        <v>216</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>326</v>
       </c>
       <c r="R57" t="n">
-        <v>567</v>
+        <v>542</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5778,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1264211104</t>
+          <t>1342897161</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264211104</t>
+          <t>https://m.place.naver.com/place/1342897161</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5804,34 +5800,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아트스타일네일</t>
+          <t>악어네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>gotitkorea@naver.com</t>
+          <t>bestone4848@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1418-1574</t>
+          <t>0507-1325-3157</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 30 416호</t>
+          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
+          <t>http://pf.kakao.com/_qxjdtG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5852,7 +5848,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5861,13 +5857,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>117</v>
+        <v>307</v>
       </c>
       <c r="Q58" t="n">
-        <v>274</v>
+        <v>10</v>
       </c>
       <c r="R58" t="n">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,17 +5872,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1976908458</t>
+          <t>1369177883</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976908458</t>
+          <t>https://m.place.naver.com/place/1369177883</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5898,34 +5894,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일을기억해</t>
+          <t>블링뷰네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>rimo0904@naver.com</t>
+          <t>bv_nail@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1491-7279</t>
+          <t>0507-1350-9502</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/remember._nails</t>
+          <t>http://pf.kakao.com/_RqUxcG</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5955,13 +5951,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="Q59" t="n">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="R59" t="n">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,17 +5966,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1811328950</t>
+          <t>1259415075</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811328950</t>
+          <t>https://m.place.naver.com/place/1259415075</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5992,29 +5988,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>맑은네일&amp;오로지푸스 인천검단신도시점</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ekal5027@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1318-8700</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서로3로 50 모아미래도 엘리트파크 상가1동109호</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/malgunnail</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6029,7 +6025,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6045,17 +6041,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>414</v>
+        <v>907</v>
       </c>
       <c r="Q60" t="n">
-        <v>57</v>
+        <v>380</v>
       </c>
       <c r="R60" t="n">
-        <v>471</v>
+        <v>1287</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6064,17 +6060,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1926633328</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926633328</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6086,25 +6082,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>카밀라네일 검단신도시점</t>
+          <t>네일은</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ojolfkj@naver.com</t>
+          <t>jisoo851208@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1356-4122</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
+          <t>인천광역시 서구 가정로 451 232호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/naileun_85</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>765</v>
+        <v>192</v>
       </c>
       <c r="Q61" t="n">
-        <v>335</v>
+        <v>232</v>
       </c>
       <c r="R61" t="n">
-        <v>1100</v>
+        <v>424</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6154,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1490697723</t>
+          <t>1380582584</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490697723</t>
+          <t>https://m.place.naver.com/place/1380582584</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6176,29 +6176,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
+          <t>바리에라네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gamejaki@naver.com</t>
+          <t>rosekim1102@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1390-9307</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 바리미로5번길 8 409호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>https://www.instagram.com/varier_la_nail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6233,13 +6233,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>313</v>
+        <v>158</v>
       </c>
       <c r="Q62" t="n">
-        <v>221</v>
+        <v>38</v>
       </c>
       <c r="R62" t="n">
-        <v>534</v>
+        <v>196</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6248,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>2090298265</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/2090298265</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6270,12 +6270,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>쑤기네일</t>
+          <t>달미네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mylovetenka@naver.com</t>
+          <t>jinjoo8570@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6283,22 +6283,22 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 30 벨라미루원 1차 417호</t>
+          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssukinail</t>
+          <t>https://toss.place/_lb/aWKRY9YJt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6323,13 +6323,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="Q63" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="R63" t="n">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6338,17 +6338,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1614043169</t>
+          <t>2000818117</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614043169</t>
+          <t>https://m.place.naver.com/place/2000818117</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6360,29 +6360,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일드벨라 인천검단점</t>
+          <t>네일이음 검단신도시점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>naildebella@naver.com</t>
+          <t>slovejy@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1356-3442</t>
+          <t>0507-1373-3055</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 307호</t>
+          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildebella</t>
+          <t>https://www.instagram.com/nailieum</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6417,13 +6417,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>261</v>
+        <v>1306</v>
       </c>
       <c r="Q64" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="R64" t="n">
-        <v>296</v>
+        <v>1378</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6432,17 +6432,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1219318994</t>
+          <t>1729889261</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1219318994</t>
+          <t>https://m.place.naver.com/place/1729889261</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6454,29 +6454,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>해온네일</t>
+          <t>다린네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>cocory_snb@naver.com</t>
+          <t>merry0903_@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1368-2279</t>
+          <t>0507-1419-3567</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
+          <t>인천광역시 서구 한중로 10 메르시타워 501호(1층 메가커피건물5층)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
+          <t>https://www.instagram.com/DARIN.GLOBAL</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6507,17 +6507,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>46</v>
+        <v>212</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R65" t="n">
-        <v>62</v>
+        <v>224</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6526,17 +6526,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2095874863</t>
+          <t>1665621156</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095874863</t>
+          <t>https://m.place.naver.com/place/1665621156</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6548,29 +6548,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+          <t>1248네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01192291122@naver.com</t>
+          <t>1248nail@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1338-0068</t>
+          <t>0507-1479-8978</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/01192291122</t>
+          <t>https://www.instagram.com/1248_nail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>907</v>
+        <v>452</v>
       </c>
       <c r="Q66" t="n">
-        <v>380</v>
+        <v>267</v>
       </c>
       <c r="R66" t="n">
-        <v>1287</v>
+        <v>719</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6620,17 +6620,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1868333219</t>
+          <t>1537239618</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868333219</t>
+          <t>https://m.place.naver.com/place/1537239618</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6642,29 +6642,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일달다 청라점</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>haru_log_in@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1325-3255</t>
+          <t>0507-1346-5358</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildalda_</t>
+          <t>https://www.instagram.com/nail.grimmy</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>608</v>
+        <v>349</v>
       </c>
       <c r="Q67" t="n">
-        <v>230</v>
+        <v>54</v>
       </c>
       <c r="R67" t="n">
-        <v>838</v>
+        <v>403</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6714,17 +6714,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1040857451</t>
+          <t>1125220368</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040857451</t>
+          <t>https://m.place.naver.com/place/1125220368</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6736,29 +6736,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일위드유 문제성발톱 속눈썹</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>nail_with_yoo@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1344-1735</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_with_yoo</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6793,13 +6793,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>257</v>
+        <v>611</v>
       </c>
       <c r="Q68" t="n">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="R68" t="n">
-        <v>286</v>
+        <v>829</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6808,17 +6808,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1776289071</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776289071</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6830,34 +6830,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일갱 인천검단점</t>
+          <t>온다네일룸</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>nailgang_@naver.com</t>
+          <t>dl7246@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1353-4100</t>
+          <t>0507-1369-7246</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
+          <t>인천광역시 서구 완정로 179 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bJxdCG</t>
+          <t>https://www.instagram.com/onda_nail_room/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6878,7 +6878,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6887,13 +6887,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1684</v>
+        <v>751</v>
       </c>
       <c r="Q69" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="R69" t="n">
-        <v>1715</v>
+        <v>797</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6902,17 +6902,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1098311831</t>
+          <t>1656364709</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098311831</t>
+          <t>https://m.place.naver.com/place/1656364709</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6924,25 +6924,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일바연</t>
+          <t>네일희 검단신도시점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yeerina@naver.com</t>
+          <t>gosm06@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1398-9916</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
+          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.by.yeon</t>
+          <t>https://www.instagram.com/_nailhee_</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6977,13 +6981,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>678</v>
+        <v>343</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R70" t="n">
-        <v>703</v>
+        <v>358</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6992,17 +6996,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1017865788</t>
+          <t>1280546741</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017865788</t>
+          <t>https://m.place.naver.com/place/1280546741</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7014,29 +7018,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>손끝한올네일</t>
+          <t>젤로미네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ouo6973@naver.com</t>
+          <t>nailjellomi@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1392-5639</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로 17 2층 203호</t>
+          <t>인천광역시 서구 검단로 480 3층 305호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
+          <t>https://www.instagram.com/nail._.jellomi</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7071,13 +7071,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="Q71" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="R71" t="n">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7086,17 +7086,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2013624857</t>
+          <t>2051638884</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013624857</t>
+          <t>https://m.place.naver.com/place/2051638884</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7108,29 +7108,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일무디크</t>
+          <t>라벨르뷰티</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>labelle0322@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1375-3428</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_moodique</t>
+          <t>https://www.instagram.com/la__belle_beauty</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7165,13 +7161,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>167</v>
+        <v>1114</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>252</v>
       </c>
       <c r="R72" t="n">
-        <v>176</v>
+        <v>1366</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7180,17 +7176,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1811715033</t>
+          <t>1968058232</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811715033</t>
+          <t>https://m.place.naver.com/place/1968058232</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7202,29 +7198,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>네일도빛나</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>sjh888347@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1302-9518</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 승학로 551 동곡프라자 1층 107호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>https://www.instagram.com/naildo_bitna</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7239,7 +7235,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7259,13 +7255,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>319</v>
+        <v>476</v>
       </c>
       <c r="Q73" t="n">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="R73" t="n">
-        <v>435</v>
+        <v>571</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7274,17 +7270,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1239607974</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1239607974</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7296,29 +7292,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일이음 검단신도시점</t>
+          <t>감성네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>slovejy@naver.com</t>
+          <t>gamseongnail@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1373-3055</t>
+          <t>0507-1424-4545</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailieum</t>
+          <t>https://www.instagram.com/gam_seongnail/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7353,13 +7349,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1281</v>
+        <v>447</v>
       </c>
       <c r="Q74" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="R74" t="n">
-        <v>1349</v>
+        <v>612</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7368,17 +7364,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1729889261</t>
+          <t>1382824710</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729889261</t>
+          <t>https://m.place.naver.com/place/1382824710</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7390,29 +7386,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>반스뷰티&amp;네일 청라점</t>
+          <t>레푸스검단점&amp;로브</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>dkfma48007@naver.com</t>
+          <t>refussgumdan@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1373-7577</t>
+          <t>0507-1345-7844</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 비즈니스로 165 청라모아미래도아파트단지내상가 2층</t>
+          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ban_s_beauty?igsh=cmI3djEyOXJjcGJm</t>
+          <t>https://www.instagram.com/refuss_gumdan</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7438,7 +7434,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7447,13 +7443,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="Q75" t="n">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="R75" t="n">
-        <v>296</v>
+        <v>661</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7462,17 +7458,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1751652203</t>
+          <t>1967477084</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1751652203</t>
+          <t>https://m.place.naver.com/place/1967477084</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7484,29 +7480,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>소담뷰티 검단신도시점</t>
+          <t>오오샵 검단점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>on323652@naver.com</t>
+          <t>dhaldud10@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1484-9220</t>
+          <t>070-4062-0556</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
+          <t>인천광역시 서구 완정로 159 1층 105호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sodam_beauty1</t>
+          <t>https://www.instagram.com/55_allinone_shop/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7541,13 +7537,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>210</v>
+        <v>618</v>
       </c>
       <c r="Q76" t="n">
-        <v>318</v>
+        <v>25</v>
       </c>
       <c r="R76" t="n">
-        <v>528</v>
+        <v>643</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7556,17 +7552,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1342897161</t>
+          <t>1739642099</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342897161</t>
+          <t>https://m.place.naver.com/place/1739642099</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/서구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서구_네일샵.xlsx
@@ -421,8 +421,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,34 +564,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>tory0413@naver.com</t>
-        </is>
-      </c>
+          <t>오오샵 서구청점</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1332-6316</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 심곡로 44-1 108호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>https://www.instagram.com/55shop_simgock</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +593,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +613,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>663</v>
+        <v>136</v>
       </c>
       <c r="Q2" t="n">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>830</v>
+        <v>148</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +628,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>1488480006</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/1488480006</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -658,29 +650,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>네일이음 검단신도시점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>slovejy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>0507-1373-3055</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>https://www.instagram.com/nailieum</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +687,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>570</v>
+        <v>1310</v>
       </c>
       <c r="Q3" t="n">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="R3" t="n">
-        <v>704</v>
+        <v>1382</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>1729889261</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/1729889261</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -752,29 +744,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미엘네일브로우 인천가정점</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mielnailbrow@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1355-4026</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mielnailbrow_</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +781,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +797,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>730</v>
+        <v>907</v>
       </c>
       <c r="Q4" t="n">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="R4" t="n">
-        <v>1127</v>
+        <v>1287</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>409746804</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/409746804</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -846,34 +838,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일으니크</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rohyunji8442@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1394-1471</t>
+          <t>0507-1344-1735</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjfJWG</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +886,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>429</v>
+        <v>258</v>
       </c>
       <c r="Q5" t="n">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="R5" t="n">
-        <v>516</v>
+        <v>287</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1466509562</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466509562</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -940,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뷰티드시엘</t>
+          <t>바리에라네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jysjysyessle@naver.com</t>
+          <t>rosekim1102@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1448-4452</t>
+          <t>0507-1390-9307</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
+          <t>인천광역시 서구 바리미로5번길 8 409호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_du_ciel</t>
+          <t>https://www.instagram.com/varier_la_nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="R6" t="n">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1538853353</t>
+          <t>2090298265</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538853353</t>
+          <t>https://m.place.naver.com/place/2090298265</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1026,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레푸스 청라점</t>
+          <t>네일도속눈썹</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dldeoqkr@naver.com</t>
+          <t>naildorash1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1337-0812</t>
+          <t>0507-1395-6008</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+          <t>인천광역시 서구 염곡로 346-1 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYKKOFJe</t>
+          <t>http://instagram.com/naildo_lash</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>296</v>
+        <v>404</v>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>289</v>
       </c>
       <c r="R7" t="n">
-        <v>364</v>
+        <v>693</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1742485791</t>
+          <t>1958392738</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742485791</t>
+          <t>https://m.place.naver.com/place/1958392738</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1120,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>mobi04@naver.com</t>
-        </is>
-      </c>
+          <t>카밀라네일 검단신도시점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1398-8291</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>573</v>
+        <v>757</v>
       </c>
       <c r="Q8" t="n">
-        <v>834</v>
+        <v>360</v>
       </c>
       <c r="R8" t="n">
-        <v>1407</v>
+        <v>1117</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>1490697723</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/1490697723</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1206,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일도속눈썹</t>
+          <t>소담뷰티 검단신도시점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>naildorash1@naver.com</t>
+          <t>on323652@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1395-6008</t>
+          <t>0507-1484-9220</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로 346-1 1층</t>
+          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildo_lash</t>
+          <t>https://www.instagram.com/sodam_beauty1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1254,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>404</v>
+        <v>219</v>
       </c>
       <c r="Q9" t="n">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="R9" t="n">
-        <v>693</v>
+        <v>544</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1958392738</t>
+          <t>1342897161</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958392738</t>
+          <t>https://m.place.naver.com/place/1342897161</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1316,34 +1300,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일벨</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>nailbelle@naver.com</t>
-        </is>
-      </c>
+          <t>아이퀸네일 청라점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1324-7499</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원창로229번길 39 1층</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Nmwmxb</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1364,7 +1344,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1353,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="Q10" t="n">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="R10" t="n">
-        <v>353</v>
+        <v>550</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1368,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1895861710</t>
+          <t>1330577008</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895861710</t>
+          <t>https://m.place.naver.com/place/1330577008</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1390,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에스영이네일</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>s02nail@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1322-9488</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JAxdFs</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1458,7 +1438,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1447,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>426</v>
+        <v>611</v>
       </c>
       <c r="Q11" t="n">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="R11" t="n">
-        <v>614</v>
+        <v>829</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1726483094</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726483094</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1504,25 +1484,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>루미온네일 검단신도시점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>네일무우 인천검단점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>n_mou@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1347-5944</t>
+          <t>0507-1382-9824</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
+          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
+          <t>https://blog.naver.com/n_mou</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,7 +1521,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,13 +1541,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36</v>
+        <v>326</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>340</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1556,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2012993603</t>
+          <t>1965956470</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012993603</t>
+          <t>https://m.place.naver.com/place/1965956470</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1578,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>루비네일</t>
+          <t>풋라인 / 발각질 무좀발톱 손톱 내성발톱</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ruby1004_mj@naver.com</t>
+          <t>footline_@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1486-3019</t>
+          <t>0507-1413-5896</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
+          <t>인천광역시 서구 서곶로 50 3동 2층 B226호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rubynail3006</t>
+          <t>https://blog.naver.com/footline_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,17 +1631,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>279</v>
+        <v>91</v>
       </c>
       <c r="Q13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="R13" t="n">
-        <v>339</v>
+        <v>131</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1650,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1233475580</t>
+          <t>1082466960</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233475580</t>
+          <t>https://m.place.naver.com/place/1082466960</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1688,34 +1672,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일위드유 문제성발톱 속눈썹</t>
+          <t>제이언니네 청라본점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nail_with_yoo@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1344-1735</t>
+          <t>0507-1332-6316</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_with_yoo</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1745,13 +1729,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>258</v>
+        <v>663</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="R14" t="n">
-        <v>287</v>
+        <v>830</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1744,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1776289071</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776289071</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1766,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일글로우</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>cottonpp@naver.com</t>
-        </is>
-      </c>
+          <t>온다네일룸</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1460-8342</t>
+          <t>0507-1369-7246</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
+          <t>인천광역시 서구 완정로 179 3층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/onda_nail_room/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1839,13 +1819,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>63</v>
+        <v>753</v>
       </c>
       <c r="Q15" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="R15" t="n">
-        <v>120</v>
+        <v>799</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2075971036</t>
+          <t>1656364709</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075971036</t>
+          <t>https://m.place.naver.com/place/1656364709</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1876,29 +1856,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1913,7 +1893,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1933,13 +1913,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>615</v>
+        <v>212</v>
       </c>
       <c r="Q16" t="n">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>746</v>
+        <v>220</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1928,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1950,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일을기억해</t>
+          <t>네일드벨라 인천검단점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rimo0904@naver.com</t>
+          <t>naildebella@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1491-7279</t>
+          <t>0507-1356-3442</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+          <t>인천광역시 서구 이음대로 384 307호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/remember._nails</t>
+          <t>https://blog.naver.com/naildebella</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2007,7 +1987,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2018,7 +1998,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2027,13 +2007,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="Q17" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R17" t="n">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1811328950</t>
+          <t>1219318994</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811328950</t>
+          <t>https://m.place.naver.com/place/1219318994</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2064,34 +2044,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>신스티니네일</t>
+          <t>소요뷰티</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jin70826@naver.com</t>
+          <t>raindrop3113@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1399-4665</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
+          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_tkuSxj</t>
+          <t>https://www.instagram.com/soyo._.beauty</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2112,7 +2088,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2097,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1138</v>
+        <v>573</v>
       </c>
       <c r="Q18" t="n">
-        <v>843</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1981</v>
+        <v>578</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2112,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1503407402</t>
+          <t>1142806255</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503407402</t>
+          <t>https://m.place.naver.com/place/1142806255</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2158,34 +2134,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>라라뷰티</t>
+          <t>네일바연</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rmatnr0203@naver.com</t>
+          <t>yeerina@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1446-6698</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 481 301호</t>
+          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__lalabeauty__</t>
+          <t>http://instagram.com/nail.by.yeon</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2195,7 +2167,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2215,13 +2187,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>632</v>
+        <v>687</v>
       </c>
       <c r="Q19" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>671</v>
+        <v>712</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2202,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1220420271</t>
+          <t>1017865788</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220420271</t>
+          <t>https://m.place.naver.com/place/1017865788</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2224,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일달다 청라점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>haru_log_in@naver.com</t>
-        </is>
-      </c>
+          <t>네일하롱</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1325-3255</t>
+          <t>0507-1438-1442</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildalda_</t>
+          <t>https://www.instagram.com/nail._.harong</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2309,13 +2277,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="Q20" t="n">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="R20" t="n">
-        <v>860</v>
+        <v>570</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2292,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1040857451</t>
+          <t>1264211104</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040857451</t>
+          <t>https://m.place.naver.com/place/1264211104</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2346,34 +2314,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일드벨라 인천검단점</t>
+          <t>신스티니네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>naildebella@naver.com</t>
+          <t>jin70826@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1356-3442</t>
+          <t>0507-1399-4665</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 307호</t>
+          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildebella</t>
+          <t>http://pf.kakao.com/_tkuSxj</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2383,7 +2351,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2394,7 +2362,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2403,13 +2371,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>263</v>
+        <v>1139</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>844</v>
       </c>
       <c r="R21" t="n">
-        <v>299</v>
+        <v>1983</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2386,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1219318994</t>
+          <t>1503407402</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1219318994</t>
+          <t>https://m.place.naver.com/place/1503407402</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2440,34 +2408,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일델루나</t>
+          <t>레푸스 청라점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>eatingzzz@naver.com</t>
+          <t>dldeoqkr@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1358-7017</t>
+          <t>0507-1337-0812</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_delluna</t>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2488,7 +2456,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2497,13 +2465,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1523</v>
+        <v>296</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="R22" t="n">
-        <v>1538</v>
+        <v>364</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2480,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1852644091</t>
+          <t>1742485791</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852644091</t>
+          <t>https://m.place.naver.com/place/1742485791</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2534,29 +2502,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>gamejaki@naver.com</t>
+          <t>mobi04@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1398-8291</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2591,13 +2559,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>314</v>
+        <v>572</v>
       </c>
       <c r="Q23" t="n">
-        <v>236</v>
+        <v>837</v>
       </c>
       <c r="R23" t="n">
-        <v>550</v>
+        <v>1409</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,17 +2574,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>1090442730</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/1090442730</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2628,29 +2596,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>맑은네일&amp;오로지푸스 인천검단신도시점</t>
+          <t>포네하네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ekal5027@naver.com</t>
+          <t>forestnh@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1318-8700</t>
+          <t>0507-1400-8523</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서로3로 50 모아미래도 엘리트파크 상가1동109호</t>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/malgunnail</t>
+          <t>https://blog.naver.com/forestnh</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2665,7 +2633,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2685,13 +2653,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>416</v>
+        <v>331</v>
       </c>
       <c r="Q24" t="n">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="R24" t="n">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,17 +2668,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1926633328</t>
+          <t>1672609930</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926633328</t>
+          <t>https://m.place.naver.com/place/1672609930</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2722,29 +2690,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일또온나 청라점</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2xmania2xj@naver.com</t>
-        </is>
-      </c>
+          <t>손끝한올네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1338-3150</t>
+          <t>0507-1392-5639</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+          <t>인천광역시 서구 바리미로 17 2층 203호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_tto_onna</t>
+          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2779,13 +2743,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>247</v>
+        <v>76</v>
       </c>
       <c r="Q25" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
-        <v>310</v>
+        <v>94</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,17 +2758,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1546215593</t>
+          <t>2013624857</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546215593</t>
+          <t>https://m.place.naver.com/place/2013624857</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2816,29 +2780,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>와우뷰티 청라점</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>e5174@naver.com</t>
-        </is>
-      </c>
+          <t>라벨르뷰티</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1323-1043</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/la__belle_beauty</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2873,13 +2829,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>91</v>
+        <v>1114</v>
       </c>
       <c r="Q26" t="n">
-        <v>48</v>
+        <v>253</v>
       </c>
       <c r="R26" t="n">
-        <v>139</v>
+        <v>1367</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,17 +2844,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1012993987</t>
+          <t>1968058232</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012993987</t>
+          <t>https://m.place.naver.com/place/1968058232</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2910,44 +2866,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일무우 인천검단점</t>
+          <t>달미네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>n_mou@naver.com</t>
+          <t>jinjoo8570@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1382-9824</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
+          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/n_mou</t>
+          <t>https://toss.place/_lb/aWKRY9YJt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2967,13 +2919,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>326</v>
+        <v>200</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>340</v>
+        <v>210</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,17 +2934,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1965956470</t>
+          <t>2000818117</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965956470</t>
+          <t>https://m.place.naver.com/place/2000818117</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3004,34 +2956,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>이루아네일</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>nec1153@naver.com</t>
-        </is>
-      </c>
+          <t>네일글로우</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1460-8342</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3061,13 +3009,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="R28" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,17 +3024,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>2075971036</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/2075971036</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3098,25 +3046,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일바연</t>
+          <t>하프네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>yeerina@naver.com</t>
+          <t>half7571@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1380-7571</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
+          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.by.yeon</t>
+          <t>https://www.instagram.com/half_nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3151,13 +3103,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>685</v>
+        <v>1610</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>191</v>
       </c>
       <c r="R29" t="n">
-        <v>710</v>
+        <v>1801</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,17 +3118,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1017865788</t>
+          <t>1259862588</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017865788</t>
+          <t>https://m.place.naver.com/place/1259862588</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3188,34 +3140,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일하고가람</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>dkfzhdspdlf@naver.com</t>
-        </is>
-      </c>
+          <t>악어네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1468-0177</t>
+          <t>0507-1325-3157</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
+          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailharam_</t>
+          <t>http://pf.kakao.com/_qxjdtG</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3236,7 +3184,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3245,13 +3193,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>106</v>
+        <v>308</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R30" t="n">
-        <v>126</v>
+        <v>318</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,17 +3208,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1958882228</t>
+          <t>1369177883</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958882228</t>
+          <t>https://m.place.naver.com/place/1369177883</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3282,29 +3230,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일하롱</t>
+          <t>네일또온나 청라점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mimmmm95_@naver.com</t>
+          <t>2xmania2xj@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1438-1442</t>
+          <t>0507-1338-3150</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.harong</t>
+          <t>https://www.instagram.com/nail_tto_onna</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3339,13 +3287,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>534</v>
+        <v>247</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="R31" t="n">
-        <v>570</v>
+        <v>310</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,17 +3302,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1264211104</t>
+          <t>1546215593</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264211104</t>
+          <t>https://m.place.naver.com/place/1546215593</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3376,25 +3324,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일인유</t>
+          <t>1248네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bonheur0118@naver.com</t>
+          <t>1248nail@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1479-8978</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inyou</t>
+          <t>https://www.instagram.com/1248_nail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3429,13 +3381,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1182</v>
+        <v>453</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>267</v>
       </c>
       <c r="R32" t="n">
-        <v>1197</v>
+        <v>720</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3396,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1117254073</t>
+          <t>1537239618</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117254073</t>
+          <t>https://m.place.naver.com/place/1537239618</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3418,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>하프네일</t>
+          <t>감성네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>half7571@naver.com</t>
+          <t>gamseongnail@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1380-7571</t>
+          <t>0507-1424-4545</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/half_nail</t>
+          <t>https://www.instagram.com/gam_seongnail/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3523,13 +3475,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1610</v>
+        <v>448</v>
       </c>
       <c r="Q33" t="n">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="R33" t="n">
-        <v>1801</v>
+        <v>612</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3490,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1259862588</t>
+          <t>1382824710</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259862588</t>
+          <t>https://m.place.naver.com/place/1382824710</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3560,25 +3512,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>카밀라네일 검단신도시점</t>
+          <t>루미온네일 검단신도시점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ojolfkj@naver.com</t>
+          <t>myeongmy1012@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1347-5944</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
+          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3613,13 +3569,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>758</v>
+        <v>36</v>
       </c>
       <c r="Q34" t="n">
-        <v>358</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>1116</v>
+        <v>43</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3584,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1490697723</t>
+          <t>2012993603</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490697723</t>
+          <t>https://m.place.naver.com/place/2012993603</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3650,34 +3606,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일디핀</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>sina1310@naver.com</t>
-        </is>
-      </c>
+          <t>이루아네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1476-4029</t>
+          <t>0507-1400-0973</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildeepin</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3707,13 +3659,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R35" t="n">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,17 +3674,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2047454568</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047454568</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3744,29 +3696,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>손끝한올네일</t>
+          <t>젤로미네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ouo6973@naver.com</t>
+          <t>nailjellomi@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0507-1392-5639</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로 17 2층 203호</t>
+          <t>인천광역시 서구 검단로 480 3층 305호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
+          <t>https://www.instagram.com/nail._.jellomi</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3801,13 +3749,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="R36" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,17 +3764,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2013624857</t>
+          <t>2051638884</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013624857</t>
+          <t>https://m.place.naver.com/place/2051638884</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3838,29 +3786,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>네일인유</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>bonheur0118@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0507-1309-5041</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+          <t>https://www.instagram.com/nail_inyou</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3895,13 +3839,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>212</v>
+        <v>1182</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="R37" t="n">
-        <v>220</v>
+        <v>1197</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,17 +3854,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1024146721</t>
+          <t>1117254073</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024146721</t>
+          <t>https://m.place.naver.com/place/1117254073</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3932,29 +3876,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>mielnailbrow@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1355-4026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>https://www.instagram.com/mielnailbrow_</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3969,7 +3913,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3989,13 +3933,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>330</v>
+        <v>731</v>
       </c>
       <c r="Q38" t="n">
-        <v>116</v>
+        <v>401</v>
       </c>
       <c r="R38" t="n">
-        <v>446</v>
+        <v>1132</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4004,17 +3948,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>409746804</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/409746804</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4026,25 +3970,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>도르네일</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>bnm4818@naver.com</t>
-        </is>
-      </c>
+          <t>네일으니크</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1394-1471</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/hCmFKNexK</t>
+          <t>https://pf.kakao.com/_xjfJWG</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4054,7 +3998,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4070,7 +4014,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4079,13 +4023,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>719</v>
+        <v>430</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="R39" t="n">
-        <v>772</v>
+        <v>518</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,17 +4038,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1001824596</t>
+          <t>1466509562</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001824596</t>
+          <t>https://m.place.naver.com/place/1466509562</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4116,30 +4060,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일에딧</t>
+          <t>네일무디크</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>byddooroo@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1375-3428</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dZxhxcn</t>
+          <t>https://www.instagram.com/nail_moodique</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4160,7 +4108,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4169,13 +4117,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>778</v>
+        <v>168</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>784</v>
+        <v>177</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4184,17 +4132,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2041818773</t>
+          <t>1811715033</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041818773</t>
+          <t>https://m.place.naver.com/place/1811715033</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4206,29 +4154,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일무디크</t>
+          <t>네일희 검단신도시점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>gosm06@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1375-3428</t>
+          <t>0507-1398-9916</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_moodique</t>
+          <t>https://www.instagram.com/_nailhee_</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4263,13 +4211,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>168</v>
+        <v>343</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R41" t="n">
-        <v>177</v>
+        <v>358</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4278,17 +4226,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1811715033</t>
+          <t>1280546741</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811715033</t>
+          <t>https://m.place.naver.com/place/1280546741</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4300,29 +4248,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>라나뷰티 청라본점</t>
+          <t>아트스타일네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>gotitkorea@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1392-1325</t>
+          <t>0507-1418-1574</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+          <t>인천광역시 서구 염곡로464번길 30 416호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_rananail</t>
+          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4348,7 +4296,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4357,13 +4305,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>459</v>
+        <v>116</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>291</v>
       </c>
       <c r="R42" t="n">
-        <v>484</v>
+        <v>407</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4320,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1071013615</t>
+          <t>1976908458</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071013615</t>
+          <t>https://m.place.naver.com/place/1976908458</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4394,34 +4342,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일갱 인천검단점</t>
+          <t>루비네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nailgang_@naver.com</t>
+          <t>ruby1004_mj@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1353-4100</t>
+          <t>0507-1486-3019</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
+          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bJxdCG</t>
+          <t>https://www.instagram.com/rubynail3006</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4442,7 +4390,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4451,13 +4399,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1695</v>
+        <v>279</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="R43" t="n">
-        <v>1726</v>
+        <v>340</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,17 +4414,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1098311831</t>
+          <t>1233475580</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098311831</t>
+          <t>https://m.place.naver.com/place/1233475580</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4488,34 +4436,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아트스타일네일</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>gotitkorea@naver.com</t>
-        </is>
-      </c>
+          <t>이르미네일</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1418-1574</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 30 416호</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4536,7 +4480,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4545,13 +4489,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>116</v>
+        <v>234</v>
       </c>
       <c r="Q44" t="n">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="R44" t="n">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4560,17 +4504,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1976908458</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976908458</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4582,29 +4526,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>오늘도네일도</t>
+          <t>뉴아네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nail_oneul@naver.com</t>
+          <t>wlsdl2102@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1449-7506</t>
+          <t>0507-1336-2796</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+          <t>인천광역시 서구 승학로 418 101호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_oneul</t>
+          <t>https://www.instagram.com/newa_nail25</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4619,7 +4563,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4639,13 +4583,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>812</v>
+        <v>88</v>
       </c>
       <c r="Q45" t="n">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="R45" t="n">
-        <v>854</v>
+        <v>213</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4654,17 +4598,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1810678383</t>
+          <t>1799034051</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810678383</t>
+          <t>https://m.place.naver.com/place/1799034051</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4676,29 +4620,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>인생네일 청라본점</t>
+          <t>제이제이네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>askflclsrna@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1301-5228</t>
+          <t>0507-1319-1270</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/life_nail_salon</t>
+          <t>https://www.instagram.com/jj__nail___</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4733,13 +4677,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>350</v>
+        <v>96</v>
       </c>
       <c r="Q46" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>361</v>
+        <v>99</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4748,17 +4692,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1764464663</t>
+          <t>2011413114</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764464663</t>
+          <t>https://m.place.naver.com/place/2011413114</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4770,34 +4714,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>무드온네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>llggggll@naver.com</t>
-        </is>
-      </c>
+          <t>오늘의기분 네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1494-6716</t>
+          <t>0507-1307-8929</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moodon.nail</t>
+          <t>http://pf.kakao.com/_pxcsgb</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4818,7 +4758,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4827,13 +4767,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>46</v>
+        <v>349</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="R47" t="n">
-        <v>57</v>
+        <v>426</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4842,17 +4782,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2044601280</t>
+          <t>1747055394</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044601280</t>
+          <t>https://m.place.naver.com/place/1747055394</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4864,34 +4804,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
+          <t>네일도빛나</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bae_tamine@naver.com</t>
+          <t>sjh888347@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1302-9518</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 승학로 551 동곡프라자 1층 107호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>https://www.instagram.com/naildo_bitna</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4912,7 +4852,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4921,13 +4861,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>347</v>
+        <v>477</v>
       </c>
       <c r="Q48" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="R48" t="n">
-        <v>424</v>
+        <v>572</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4876,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>1239607974</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/1239607974</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4958,29 +4898,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>뉴아네일</t>
+          <t>섬세하나네일 청라본점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>wlsdl2102@naver.com</t>
+          <t>sumsehana@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1336-2796</t>
+          <t>0507-1481-0788</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 418 101호</t>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newa_nail25</t>
+          <t>https://blog.naver.com/sumsehana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4995,7 +4935,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5015,13 +4955,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>88</v>
+        <v>615</v>
       </c>
       <c r="Q49" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="R49" t="n">
-        <v>212</v>
+        <v>746</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +4970,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1799034051</t>
+          <t>1251340543</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799034051</t>
+          <t>https://m.place.naver.com/place/1251340543</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5052,29 +4992,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>제이제이네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1319-1270</t>
+          <t>0507-1346-5358</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jj__nail___</t>
+          <t>https://www.instagram.com/nail.grimmy</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5109,13 +5049,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>95</v>
+        <v>349</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="R50" t="n">
-        <v>98</v>
+        <v>403</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5064,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2011413114</t>
+          <t>1125220368</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011413114</t>
+          <t>https://m.place.naver.com/place/1125220368</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5146,29 +5086,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>이르미네일</t>
+          <t>네일에딧</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>aboutdanchuu@naver.com</t>
+          <t>byddooroo@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1391-3129</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ezxgrG</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5203,13 +5139,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>234</v>
+        <v>781</v>
       </c>
       <c r="Q51" t="n">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="R51" t="n">
-        <v>341</v>
+        <v>787</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5154,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1596414337</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596414337</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5240,34 +5176,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>dodofamily_mam@naver.com</t>
-        </is>
-      </c>
+          <t>에스영이네일</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1322-9488</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>http://pf.kakao.com/_JAxdFs</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5288,7 +5220,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5297,13 +5229,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="R52" t="n">
-        <v>446</v>
+        <v>614</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5244,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1726483094</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1726483094</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5334,29 +5266,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>단감네일</t>
+          <t>라나뷰티 청라본점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>aayoon7@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1374-8432</t>
+          <t>0507-1392-1325</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dangam_nail/</t>
+          <t>https://www.instagram.com/_rananail</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5382,7 +5314,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5391,13 +5323,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>205</v>
+        <v>459</v>
       </c>
       <c r="Q53" t="n">
-        <v>337</v>
+        <v>25</v>
       </c>
       <c r="R53" t="n">
-        <v>542</v>
+        <v>484</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5338,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1985862694</t>
+          <t>1071013615</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985862694</t>
+          <t>https://m.place.naver.com/place/1071013615</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5428,25 +5360,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>소요뷰티</t>
+          <t>라라뷰티</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>raindrop3113@naver.com</t>
+          <t>rmatnr0203@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1446-6698</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
+          <t>인천광역시 서구 승학로 481 301호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soyo._.beauty</t>
+          <t>https://www.instagram.com/__lalabeauty__</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5481,13 +5417,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>573</v>
+        <v>632</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="R54" t="n">
-        <v>578</v>
+        <v>671</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5496,17 +5432,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1142806255</t>
+          <t>1220420271</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142806255</t>
+          <t>https://m.place.naver.com/place/1220420271</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5518,29 +5454,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일,사계절</t>
+          <t>맑은네일&amp;오로지푸스 인천검단신도시점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>siryyam@naver.com</t>
+          <t>ekal5027@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1360-4822</t>
+          <t>0507-1318-8700</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
+          <t>인천광역시 서구 서로3로 50 모아미래도 엘리트파크 상가1동109호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_4season</t>
+          <t>https://www.instagram.com/malgunnail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5575,13 +5511,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>369</v>
+        <v>418</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="R55" t="n">
-        <v>377</v>
+        <v>475</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5590,17 +5526,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1216076936</t>
+          <t>1926633328</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216076936</t>
+          <t>https://m.place.naver.com/place/1926633328</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5612,34 +5548,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>해온네일</t>
+          <t>네일갱 인천검단점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>cocory_snb@naver.com</t>
+          <t>nailgang_@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1368-2279</t>
+          <t>0507-1353-4100</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
+          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
+          <t>http://pf.kakao.com/_bJxdCG</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5660,22 +5596,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>50</v>
+        <v>1696</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="R56" t="n">
-        <v>67</v>
+        <v>1727</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5684,17 +5620,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2095874863</t>
+          <t>1098311831</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095874863</t>
+          <t>https://m.place.naver.com/place/1098311831</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5706,29 +5642,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>소담뷰티 검단신도시점</t>
+          <t>프롬쥬네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>on323652@naver.com</t>
+          <t>dlaalswn89@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1484-9220</t>
+          <t>0507-1327-0666</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sodam_beauty1</t>
+          <t>https://blog.naver.com/dlaalswn89</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5743,7 +5679,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5763,13 +5699,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>216</v>
+        <v>567</v>
       </c>
       <c r="Q57" t="n">
-        <v>326</v>
+        <v>133</v>
       </c>
       <c r="R57" t="n">
-        <v>542</v>
+        <v>700</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5778,17 +5714,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1342897161</t>
+          <t>1545913000</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342897161</t>
+          <t>https://m.place.naver.com/place/1545913000</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5800,34 +5736,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>악어네일&amp;속눈썹</t>
+          <t>오오샵 검단점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bestone4848@naver.com</t>
+          <t>dhaldud10@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1325-3157</t>
+          <t>070-4062-0556</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
+          <t>인천광역시 서구 완정로 159 1층 105호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qxjdtG</t>
+          <t>https://www.instagram.com/55_allinone_shop/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5848,7 +5784,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5857,13 +5793,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>307</v>
+        <v>621</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R58" t="n">
-        <v>317</v>
+        <v>646</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5872,17 +5808,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1369177883</t>
+          <t>1739642099</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369177883</t>
+          <t>https://m.place.naver.com/place/1739642099</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5894,34 +5830,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>블링뷰네일</t>
+          <t>레푸스검단점&amp;로브</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bv_nail@naver.com</t>
+          <t>refussgumdan@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1350-9502</t>
+          <t>0507-1345-7844</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RqUxcG</t>
+          <t>https://www.instagram.com/refuss_gumdan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5942,7 +5878,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5951,13 +5887,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>117</v>
+        <v>511</v>
       </c>
       <c r="Q59" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R59" t="n">
-        <v>270</v>
+        <v>661</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5966,17 +5902,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1259415075</t>
+          <t>1967477084</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259415075</t>
+          <t>https://m.place.naver.com/place/1967477084</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5988,29 +5924,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+          <t>네일디핀</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01192291122@naver.com</t>
+          <t>sina1310@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1338-0068</t>
+          <t>0507-1476-4029</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/01192291122</t>
+          <t>https://www.instagram.com/naildeepin</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6025,7 +5961,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6041,17 +5977,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>907</v>
+        <v>85</v>
       </c>
       <c r="Q60" t="n">
-        <v>380</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>1287</v>
+        <v>92</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +5996,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1868333219</t>
+          <t>2047454568</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868333219</t>
+          <t>https://m.place.naver.com/place/2047454568</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6082,29 +6018,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일은</t>
+          <t>인생네일 청라본점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>askflclsrna@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1356-4122</t>
+          <t>0507-1301-5228</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 232호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naileun_85</t>
+          <t>https://www.instagram.com/life_nail_salon</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6139,13 +6075,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>192</v>
+        <v>350</v>
       </c>
       <c r="Q61" t="n">
-        <v>232</v>
+        <v>11</v>
       </c>
       <c r="R61" t="n">
-        <v>424</v>
+        <v>361</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6090,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1380582584</t>
+          <t>1764464663</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1380582584</t>
+          <t>https://m.place.naver.com/place/1764464663</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6176,29 +6112,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>바리에라네일</t>
+          <t>네일을기억해</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>rosekim1102@naver.com</t>
+          <t>rimo0904@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1390-9307</t>
+          <t>0507-1491-7279</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 8 409호</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/varier_la_nail</t>
+          <t>https://www.instagram.com/remember._nails</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6224,7 +6160,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6233,13 +6169,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="Q62" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="R62" t="n">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6184,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2090298265</t>
+          <t>1811328950</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090298265</t>
+          <t>https://m.place.naver.com/place/1811328950</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6270,35 +6206,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>달미네일</t>
+          <t>다린네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jinjoo8570@naver.com</t>
+          <t>merry0903_@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1419-3567</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
+          <t>인천광역시 서구 한중로 10 메르시타워 501호(1층 메가커피건물5층)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/aWKRY9YJt</t>
+          <t>https://www.instagram.com/DARIN.GLOBAL</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6323,13 +6263,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R63" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6338,17 +6278,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2000818117</t>
+          <t>1665621156</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000818117</t>
+          <t>https://m.place.naver.com/place/1665621156</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6360,29 +6300,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일이음 검단신도시점</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>slovejy@naver.com</t>
-        </is>
-      </c>
+          <t>네일하고가람</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1373-3055</t>
+          <t>0507-1468-0177</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
+          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailieum</t>
+          <t>https://www.instagram.com/nailharam_</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6417,13 +6353,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1306</v>
+        <v>106</v>
       </c>
       <c r="Q64" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="R64" t="n">
-        <v>1378</v>
+        <v>126</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6432,17 +6368,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1729889261</t>
+          <t>1958882228</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729889261</t>
+          <t>https://m.place.naver.com/place/1958882228</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6454,29 +6390,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>다린네일</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>merry0903_@naver.com</t>
-        </is>
-      </c>
+          <t>단감네일</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1419-3567</t>
+          <t>0507-1374-8432</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한중로 10 메르시타워 501호(1층 메가커피건물5층)</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/DARIN.GLOBAL</t>
+          <t>https://www.instagram.com/dangam_nail/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6511,13 +6443,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>337</v>
       </c>
       <c r="R65" t="n">
-        <v>224</v>
+        <v>542</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6526,17 +6458,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1665621156</t>
+          <t>1985862694</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1665621156</t>
+          <t>https://m.place.naver.com/place/1985862694</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6548,29 +6480,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1248네일</t>
+          <t>오늘도네일도</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1248nail@naver.com</t>
+          <t>nail_oneul@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1479-8978</t>
+          <t>0507-1449-7506</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1248_nail</t>
+          <t>https://blog.naver.com/nail_oneul</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6585,7 +6517,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6605,13 +6537,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>452</v>
+        <v>813</v>
       </c>
       <c r="Q66" t="n">
-        <v>267</v>
+        <v>42</v>
       </c>
       <c r="R66" t="n">
-        <v>719</v>
+        <v>855</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6620,17 +6552,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1537239618</t>
+          <t>1810678383</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537239618</t>
+          <t>https://m.place.naver.com/place/1810678383</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6642,34 +6574,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>네일벨</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>nailbelle@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1346-5358</t>
+          <t>0507-1324-7499</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+          <t>인천광역시 서구 원창로229번길 39 1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.grimmy</t>
+          <t>http://pf.kakao.com/_Nmwmxb</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6690,7 +6622,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6699,13 +6631,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>349</v>
+        <v>139</v>
       </c>
       <c r="Q67" t="n">
-        <v>54</v>
+        <v>215</v>
       </c>
       <c r="R67" t="n">
-        <v>403</v>
+        <v>354</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6714,17 +6646,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1125220368</t>
+          <t>1895861710</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125220368</t>
+          <t>https://m.place.naver.com/place/1895861710</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6736,29 +6668,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>dlgufl0924@naver.com</t>
-        </is>
-      </c>
+          <t>무드온네일</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1408-0807</t>
+          <t>0507-1494-6716</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lantienail_official/</t>
+          <t>https://www.instagram.com/moodon.nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6793,13 +6721,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>611</v>
+        <v>49</v>
       </c>
       <c r="Q68" t="n">
-        <v>218</v>
+        <v>13</v>
       </c>
       <c r="R68" t="n">
-        <v>829</v>
+        <v>62</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6808,17 +6736,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>37922472</t>
+          <t>2044601280</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37922472</t>
+          <t>https://m.place.naver.com/place/2044601280</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6830,29 +6758,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>온다네일룸</t>
+          <t>네일달다 청라점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>dl7246@naver.com</t>
+          <t>haru_log_in@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1369-7246</t>
+          <t>0507-1325-3255</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 179 3층</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onda_nail_room/</t>
+          <t>http://instagram.com/naildalda_</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6887,13 +6815,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>751</v>
+        <v>622</v>
       </c>
       <c r="Q69" t="n">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="R69" t="n">
-        <v>797</v>
+        <v>861</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6902,17 +6830,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1656364709</t>
+          <t>1040857451</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656364709</t>
+          <t>https://m.place.naver.com/place/1040857451</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6924,29 +6852,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일희 검단신도시점</t>
+          <t>해온네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>gosm06@naver.com</t>
+          <t>cocory_snb@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1398-9916</t>
+          <t>0507-1368-2279</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
+          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailhee_</t>
+          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6977,17 +6905,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>343</v>
+        <v>50</v>
       </c>
       <c r="Q70" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R70" t="n">
-        <v>358</v>
+        <v>67</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6996,17 +6924,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1280546741</t>
+          <t>2095874863</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280546741</t>
+          <t>https://m.place.naver.com/place/2095874863</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7018,25 +6946,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>젤로미네일</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>nailjellomi@naver.com</t>
-        </is>
-      </c>
+          <t>네일,사계절</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1360-4822</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 3층 305호</t>
+          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.jellomi</t>
+          <t>https://www.instagram.com/nail_4season</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7071,13 +6999,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>89</v>
+        <v>369</v>
       </c>
       <c r="Q71" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>137</v>
+        <v>377</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7086,17 +7014,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2051638884</t>
+          <t>1216076936</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051638884</t>
+          <t>https://m.place.naver.com/place/1216076936</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7108,25 +7036,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>라벨르뷰티</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>labelle0322@naver.com</t>
-        </is>
-      </c>
+          <t>와우뷰티 청라점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1323-1043</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la__belle_beauty</t>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7161,13 +7089,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1114</v>
+        <v>91</v>
       </c>
       <c r="Q72" t="n">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="R72" t="n">
-        <v>1366</v>
+        <v>140</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,17 +7104,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1968058232</t>
+          <t>1012993987</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968058232</t>
+          <t>https://m.place.naver.com/place/1012993987</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7198,29 +7126,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일도빛나</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>sjh888347@naver.com</t>
-        </is>
-      </c>
+          <t>네일델루나</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1302-9518</t>
+          <t>0507-1358-7017</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 551 동곡프라자 1층 107호</t>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_bitna</t>
+          <t>http://instagram.com/nail_delluna</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7255,13 +7179,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>476</v>
+        <v>1528</v>
       </c>
       <c r="Q73" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="R73" t="n">
-        <v>571</v>
+        <v>1543</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7270,17 +7194,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1239607974</t>
+          <t>1852644091</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239607974</t>
+          <t>https://m.place.naver.com/place/1852644091</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7292,34 +7216,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>감성네일</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>gamseongnail@naver.com</t>
-        </is>
-      </c>
+          <t>오오샵 가좌점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1424-4545</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7329,7 +7249,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7349,13 +7269,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="Q74" t="n">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="R74" t="n">
-        <v>612</v>
+        <v>446</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7364,17 +7284,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7386,39 +7306,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>레푸스검단점&amp;로브</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>refussgumdan@naver.com</t>
-        </is>
-      </c>
+          <t>도르네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1345-7844</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_gumdan</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7443,13 +7355,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>511</v>
+        <v>722</v>
       </c>
       <c r="Q75" t="n">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="R75" t="n">
-        <v>661</v>
+        <v>775</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7458,17 +7370,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1967477084</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967477084</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7480,34 +7392,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>오오샵 검단점</t>
+          <t>블링뷰네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dhaldud10@naver.com</t>
+          <t>bv_nail@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>070-4062-0556</t>
+          <t>0507-1350-9502</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 159 1층 105호</t>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop/</t>
+          <t>http://pf.kakao.com/_RqUxcG</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7528,7 +7440,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7537,13 +7449,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>618</v>
+        <v>117</v>
       </c>
       <c r="Q76" t="n">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="R76" t="n">
-        <v>643</v>
+        <v>270</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7552,17 +7464,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1739642099</t>
+          <t>1259415075</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739642099</t>
+          <t>https://m.place.naver.com/place/1259415075</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/서구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서구_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,26 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>오오샵 서구청점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>다린네일</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rodacompany@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1419-3567</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 심곡로 44-1 108호</t>
+          <t>인천광역시 서구 한중로 10 메르시타워 501호(1층 메가커피건물5층)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55shop_simgock</t>
+          <t>https://www.instagram.com/DARIN.GLOBAL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -593,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -613,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="Q2" t="n">
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -628,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1488480006</t>
+          <t>1665621156</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488480006</t>
+          <t>https://m.place.naver.com/place/1665621156</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -650,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일이음 검단신도시점</t>
+          <t>네일을기억해</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>slovejy@naver.com</t>
+          <t>rimo0904@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1373-3055</t>
+          <t>0507-1491-7279</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailieum</t>
+          <t>https://www.instagram.com/remember._nails</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -698,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -707,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1310</v>
+        <v>210</v>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="R3" t="n">
-        <v>1382</v>
+        <v>254</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1729889261</t>
+          <t>1811328950</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729889261</t>
+          <t>https://m.place.naver.com/place/1811328950</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -744,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+          <t>네일으니크</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01192291122@naver.com</t>
+          <t>mm9208291@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1338-0068</t>
+          <t>0507-1394-1471</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/01192291122</t>
+          <t>https://pf.kakao.com/_xjfJWG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -781,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -792,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>907</v>
+        <v>431</v>
       </c>
       <c r="Q4" t="n">
-        <v>380</v>
+        <v>88</v>
       </c>
       <c r="R4" t="n">
-        <v>1287</v>
+        <v>519</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1868333219</t>
+          <t>1466509562</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868333219</t>
+          <t>https://m.place.naver.com/place/1466509562</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -838,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일위드유 문제성발톱 속눈썹</t>
+          <t>네일하고가람</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nail_with_yoo@naver.com</t>
+          <t>dkfzhdspdlf@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1344-1735</t>
+          <t>0507-1468-0177</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_with_yoo</t>
+          <t>https://www.instagram.com/nailharam_</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
-        <v>287</v>
+        <v>126</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1776289071</t>
+          <t>1958882228</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776289071</t>
+          <t>https://m.place.naver.com/place/1958882228</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -932,29 +940,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바리에라네일</t>
+          <t>라벨르뷰티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rosekim1102@naver.com</t>
+          <t>labelle0322@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1390-9307</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 8 409호</t>
+          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/varier_la_nail</t>
+          <t>https://www.instagram.com/la__belle_beauty</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>162</v>
+        <v>1115</v>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="R6" t="n">
-        <v>200</v>
+        <v>1368</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2090298265</t>
+          <t>1968058232</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090298265</t>
+          <t>https://m.place.naver.com/place/1968058232</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일도속눈썹</t>
+          <t>인생네일 청라본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>naildorash1@naver.com</t>
+          <t>askflclsrna@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1395-6008</t>
+          <t>0507-1301-5228</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로 346-1 1층</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildo_lash</t>
+          <t>https://www.instagram.com/life_nail_salon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1074,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1083,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>404</v>
+        <v>351</v>
       </c>
       <c r="Q7" t="n">
-        <v>289</v>
+        <v>11</v>
       </c>
       <c r="R7" t="n">
-        <v>693</v>
+        <v>362</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1958392738</t>
+          <t>1764464663</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958392738</t>
+          <t>https://m.place.naver.com/place/1764464663</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1120,26 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>카밀라네일 검단신도시점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>제이언니네 청라본점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mina20624@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1332-6316</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1169,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>757</v>
+        <v>665</v>
       </c>
       <c r="Q8" t="n">
-        <v>360</v>
+        <v>167</v>
       </c>
       <c r="R8" t="n">
-        <v>1117</v>
+        <v>832</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1490697723</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490697723</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1206,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>소담뷰티 검단신도시점</t>
+          <t>섬세하나네일 청라본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>on323652@naver.com</t>
+          <t>sumsehana@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1484-9220</t>
+          <t>0507-1481-0788</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sodam_beauty1</t>
+          <t>https://blog.naver.com/sumsehana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1243,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1263,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>219</v>
+        <v>620</v>
       </c>
       <c r="Q9" t="n">
-        <v>325</v>
+        <v>131</v>
       </c>
       <c r="R9" t="n">
-        <v>544</v>
+        <v>751</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1342897161</t>
+          <t>1251340543</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342897161</t>
+          <t>https://m.place.naver.com/place/1251340543</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1300,25 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>네일희 검단신도시점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gosm06@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1398-9916</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>https://www.instagram.com/_nailhee_</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="Q10" t="n">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>550</v>
+        <v>359</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1368,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>1280546741</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/1280546741</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1390,39 +1406,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
+          <t>달미네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dlgufl0924@naver.com</t>
+          <t>jinjoo8570@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1408-0807</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
+          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lantienail_official/</t>
+          <t>https://toss.place/_lb/aWKRY9YJt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1447,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>611</v>
+        <v>203</v>
       </c>
       <c r="Q11" t="n">
-        <v>218</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>829</v>
+        <v>213</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37922472</t>
+          <t>2000818117</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37922472</t>
+          <t>https://m.place.naver.com/place/2000818117</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1484,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일무우 인천검단점</t>
+          <t>아트스타일네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>n_mou@naver.com</t>
+          <t>gotitkorea@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1382-9824</t>
+          <t>0507-1418-1574</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
+          <t>인천광역시 서구 염곡로464번길 30 416호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/n_mou</t>
+          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1521,7 +1533,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1541,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>326</v>
+        <v>117</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>295</v>
       </c>
       <c r="R12" t="n">
-        <v>340</v>
+        <v>412</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1556,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1965956470</t>
+          <t>1976908458</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965956470</t>
+          <t>https://m.place.naver.com/place/1976908458</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1578,29 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>풋라인 / 발각질 무좀발톱 손톱 내성발톱</t>
+          <t>무드온네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>footline_@naver.com</t>
+          <t>llggggll@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1413-5896</t>
+          <t>0507-1494-6716</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 50 3동 2층 B226호</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/footline_</t>
+          <t>https://www.instagram.com/moodon.nail</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1615,7 +1627,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1631,17 +1643,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="Q13" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1082466960</t>
+          <t>2044601280</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1082466960</t>
+          <t>https://m.place.naver.com/place/2044601280</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1672,34 +1684,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
+          <t>프롬쥬네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>dlaalswn89@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1332-6316</t>
+          <t>0507-1327-0666</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>https://blog.naver.com/dlaalswn89</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1709,7 +1721,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1729,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>663</v>
+        <v>567</v>
       </c>
       <c r="Q14" t="n">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="R14" t="n">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>1545913000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/1545913000</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1766,25 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>온다네일룸</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>오오샵 검단점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dhaldud10@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1369-7246</t>
+          <t>070-4062-0556</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 179 3층</t>
+          <t>인천광역시 서구 완정로 159 1층 105호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onda_nail_room/</t>
+          <t>https://www.instagram.com/55_allinone_shop/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>753</v>
+        <v>622</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="R15" t="n">
-        <v>799</v>
+        <v>647</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1834,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1656364709</t>
+          <t>1739642099</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656364709</t>
+          <t>https://m.place.naver.com/place/1739642099</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1856,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>네일델루나</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>eatingzzz@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1309-5041</t>
+          <t>0507-1358-7017</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+          <t>http://instagram.com/nail_delluna</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1913,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>212</v>
+        <v>1534</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
-        <v>220</v>
+        <v>1549</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1928,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1024146721</t>
+          <t>1852644091</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024146721</t>
+          <t>https://m.place.naver.com/place/1852644091</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1950,29 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일드벨라 인천검단점</t>
+          <t>루안네일 토탈뷰티 검단점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>naildebella@naver.com</t>
+          <t>luannail@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1356-3442</t>
+          <t>0507-1349-7727</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 307호</t>
+          <t>인천광역시 서구 단봉로 97-7 1층 112호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildebella</t>
+          <t>https://http//pf.kakao.com/_vALxgG</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1987,7 +2003,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1998,7 +2014,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2007,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>263</v>
+        <v>742</v>
       </c>
       <c r="Q17" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>299</v>
+        <v>745</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1219318994</t>
+          <t>1840082670</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1219318994</t>
+          <t>https://m.place.naver.com/place/1840082670</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2060,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>소요뷰티</t>
+          <t>카밀라네일 검단신도시점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>raindrop3113@naver.com</t>
+          <t>ojolfkj@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2057,12 +2073,12 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
+          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soyo._.beauty</t>
+          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2097,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>573</v>
+        <v>759</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>369</v>
       </c>
       <c r="R18" t="n">
-        <v>578</v>
+        <v>1128</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2112,17 +2128,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1142806255</t>
+          <t>1490697723</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142806255</t>
+          <t>https://m.place.naver.com/place/1490697723</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2134,30 +2150,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일바연</t>
+          <t>맑은네일&amp;오로지푸스 인천검단신도시점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yeerina@naver.com</t>
+          <t>ekal5027@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1318-8700</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
+          <t>인천광역시 서구 서로3로 50 모아미래도 엘리트파크 상가1동109호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.by.yeon</t>
+          <t>https://www.instagram.com/malgunnail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2167,7 +2187,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2187,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>687</v>
+        <v>418</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="R19" t="n">
-        <v>712</v>
+        <v>478</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2202,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1017865788</t>
+          <t>1926633328</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017865788</t>
+          <t>https://m.place.naver.com/place/1926633328</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2224,25 +2244,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일하롱</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>네일바연</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>yeerina@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1438-1442</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.harong</t>
+          <t>http://instagram.com/nail.by.yeon</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2277,13 +2297,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>534</v>
+        <v>688</v>
       </c>
       <c r="Q20" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="R20" t="n">
-        <v>570</v>
+        <v>713</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2292,17 +2312,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1264211104</t>
+          <t>1017865788</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264211104</t>
+          <t>https://m.place.naver.com/place/1017865788</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2314,34 +2334,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>신스티니네일</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jin70826@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1399-4665</t>
+          <t>0507-1344-1735</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_tkuSxj</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2362,7 +2382,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2371,13 +2391,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1139</v>
+        <v>259</v>
       </c>
       <c r="Q21" t="n">
-        <v>844</v>
+        <v>29</v>
       </c>
       <c r="R21" t="n">
-        <v>1983</v>
+        <v>288</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2386,17 +2406,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1503407402</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503407402</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2408,29 +2428,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>레푸스 청라점</t>
+          <t>네일에딧</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dldeoqkr@naver.com</t>
+          <t>byddooroo@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1337-0812</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYKKOFJe</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2465,13 +2481,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>296</v>
+        <v>801</v>
       </c>
       <c r="Q22" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>364</v>
+        <v>807</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2480,17 +2496,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1742485791</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742485791</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2575,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Q23" t="n">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="R23" t="n">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2584,7 +2600,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2596,29 +2612,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>1248네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>1248nail@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1479-8978</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>https://www.instagram.com/1248_nail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2633,7 +2649,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2653,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>331</v>
+        <v>457</v>
       </c>
       <c r="Q24" t="n">
-        <v>116</v>
+        <v>267</v>
       </c>
       <c r="R24" t="n">
-        <v>447</v>
+        <v>724</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2668,17 +2684,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1537239618</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1537239618</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2690,35 +2706,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손끝한올네일</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>도르네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>bnm4818@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1392-5639</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로 17 2층 203호</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2743,13 +2759,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>76</v>
+        <v>728</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>782</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2758,17 +2774,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2013624857</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013624857</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2780,21 +2796,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>라벨르뷰티</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>오늘도네일도</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nail_oneul@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1449-7506</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la__belle_beauty</t>
+          <t>https://blog.naver.com/nail_oneul</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2809,7 +2833,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2829,13 +2853,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1114</v>
+        <v>815</v>
       </c>
       <c r="Q26" t="n">
-        <v>253</v>
+        <v>42</v>
       </c>
       <c r="R26" t="n">
-        <v>1367</v>
+        <v>857</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2844,17 +2868,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1968058232</t>
+          <t>1810678383</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968058232</t>
+          <t>https://m.place.naver.com/place/1810678383</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2866,25 +2890,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>달미네일</t>
+          <t>악어네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jinjoo8570@naver.com</t>
+          <t>bestone4848@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1325-3157</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
+          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/aWKRY9YJt</t>
+          <t>http://pf.kakao.com/_qxjdtG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2894,7 +2922,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2910,7 +2938,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2919,13 +2947,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>200</v>
+        <v>308</v>
       </c>
       <c r="Q27" t="n">
         <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>210</v>
+        <v>318</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2934,17 +2962,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2000818117</t>
+          <t>1369177883</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000818117</t>
+          <t>https://m.place.naver.com/place/1369177883</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2956,25 +2984,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일글로우</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>네일이음 검단신도시점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>slovejy@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1460-8342</t>
+          <t>0507-1373-3055</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
+          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nailieum</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3009,13 +3041,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>64</v>
+        <v>1322</v>
       </c>
       <c r="Q28" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="R28" t="n">
-        <v>121</v>
+        <v>1394</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3024,17 +3056,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2075971036</t>
+          <t>1729889261</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075971036</t>
+          <t>https://m.place.naver.com/place/1729889261</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3046,29 +3078,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>하프네일</t>
+          <t>어레브네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>half7571@naver.com</t>
+          <t>anwlro9344@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1380-7571</t>
+          <t>0507-1354-5482</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/half_nail</t>
+          <t>https://blog.naver.com/anwlro9344</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3083,7 +3115,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3103,13 +3135,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1610</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="n">
-        <v>191</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>1801</v>
+        <v>75</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3118,17 +3150,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1259862588</t>
+          <t>1364434683</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259862588</t>
+          <t>https://m.place.naver.com/place/1364434683</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3140,25 +3172,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>악어네일&amp;속눈썹</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>이루아네일</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>nec1153@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1325-3157</t>
+          <t>0507-1400-0973</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qxjdtG</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3184,7 +3220,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3193,13 +3229,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
-        <v>318</v>
+        <v>158</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3208,17 +3244,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1369177883</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369177883</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3230,34 +3266,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일또온나 청라점</t>
+          <t>신스티니네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2xmania2xj@naver.com</t>
+          <t>jin70826@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1338-3150</t>
+          <t>0507-1399-4665</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_tto_onna</t>
+          <t>http://pf.kakao.com/_tkuSxj</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3278,7 +3314,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3287,13 +3323,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>247</v>
+        <v>1137</v>
       </c>
       <c r="Q31" t="n">
-        <v>63</v>
+        <v>845</v>
       </c>
       <c r="R31" t="n">
-        <v>310</v>
+        <v>1982</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3302,17 +3338,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1546215593</t>
+          <t>1503407402</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546215593</t>
+          <t>https://m.place.naver.com/place/1503407402</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3324,34 +3360,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1248네일</t>
+          <t>이르미네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1248nail@naver.com</t>
+          <t>aboutdanchuu@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1479-8978</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1248_nail</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3372,7 +3408,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3381,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>453</v>
+        <v>234</v>
       </c>
       <c r="Q32" t="n">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="R32" t="n">
-        <v>720</v>
+        <v>342</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3396,17 +3432,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1537239618</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537239618</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3418,29 +3454,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>감성네일</t>
+          <t>네일무우 인천검단점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gamseongnail@naver.com</t>
+          <t>n_mou@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1424-4545</t>
+          <t>0507-1382-9824</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>https://blog.naver.com/n_mou</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3455,7 +3491,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3475,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>448</v>
+        <v>327</v>
       </c>
       <c r="Q33" t="n">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="R33" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3490,17 +3526,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>1965956470</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/1965956470</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3512,29 +3548,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>루미온네일 검단신도시점</t>
+          <t>네일하롱</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>myeongmy1012@naver.com</t>
+          <t>mimmmm95_@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1347-5944</t>
+          <t>0507-1438-1442</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
+          <t>https://www.instagram.com/nail._.harong</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3569,13 +3605,13 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>536</v>
+      </c>
+      <c r="Q34" t="n">
         <v>36</v>
       </c>
-      <c r="Q34" t="n">
-        <v>7</v>
-      </c>
       <c r="R34" t="n">
-        <v>43</v>
+        <v>572</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3584,17 +3620,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2012993603</t>
+          <t>1264211104</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012993603</t>
+          <t>https://m.place.naver.com/place/1264211104</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3606,30 +3642,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>이루아네일</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>오오샵 가좌점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dodofamily_mam@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3659,13 +3699,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>136</v>
+        <v>406</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="R35" t="n">
-        <v>158</v>
+        <v>446</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3674,17 +3714,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3696,25 +3736,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>젤로미네일</t>
+          <t>소담뷰티 검단신도시점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nailjellomi@naver.com</t>
+          <t>on323652@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1484-9220</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 3층 305호</t>
+          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.jellomi</t>
+          <t>https://www.instagram.com/sodam_beauty1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3749,13 +3793,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>326</v>
       </c>
       <c r="R36" t="n">
-        <v>137</v>
+        <v>545</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3764,17 +3808,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2051638884</t>
+          <t>1342897161</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051638884</t>
+          <t>https://m.place.naver.com/place/1342897161</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3786,25 +3830,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일인유</t>
+          <t>바리에라네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bonheur0118@naver.com</t>
+          <t>rosekim1102@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1390-9307</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
+          <t>인천광역시 서구 바리미로5번길 8 409호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inyou</t>
+          <t>https://www.instagram.com/varier_la_nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3839,13 +3887,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1182</v>
+        <v>172</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
-        <v>1197</v>
+        <v>211</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3854,17 +3902,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1117254073</t>
+          <t>2090298265</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117254073</t>
+          <t>https://m.place.naver.com/place/2090298265</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3876,34 +3924,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>미엘네일브로우 인천가정점</t>
+          <t>네일갱 인천검단점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mielnailbrow@naver.com</t>
+          <t>nailgang_@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1355-4026</t>
+          <t>0507-1353-4100</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
+          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mielnailbrow_</t>
+          <t>http://pf.kakao.com/_bJxdCG</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3924,7 +3972,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3933,13 +3981,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>731</v>
+        <v>1700</v>
       </c>
       <c r="Q38" t="n">
-        <v>401</v>
+        <v>31</v>
       </c>
       <c r="R38" t="n">
-        <v>1132</v>
+        <v>1731</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3948,17 +3996,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>409746804</t>
+          <t>1098311831</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/409746804</t>
+          <t>https://m.place.naver.com/place/1098311831</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3970,30 +4018,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일으니크</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>네일인유</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bonheur0118@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1394-1471</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
+          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjfJWG</t>
+          <t>https://www.instagram.com/nail_inyou</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4014,7 +4062,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4023,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>430</v>
+        <v>1186</v>
       </c>
       <c r="Q39" t="n">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="R39" t="n">
-        <v>518</v>
+        <v>1201</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4038,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1466509562</t>
+          <t>1117254073</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466509562</t>
+          <t>https://m.place.naver.com/place/1117254073</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4060,29 +4108,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일무디크</t>
+          <t>온다네일룸</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>dl7246@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1375-3428</t>
+          <t>0507-1369-7246</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+          <t>인천광역시 서구 완정로 179 3층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_moodique</t>
+          <t>https://www.instagram.com/onda_nail_room/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4117,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>168</v>
+        <v>755</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="R40" t="n">
-        <v>177</v>
+        <v>801</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4132,17 +4180,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1811715033</t>
+          <t>1656364709</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811715033</t>
+          <t>https://m.place.naver.com/place/1656364709</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4154,29 +4202,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일희 검단신도시점</t>
+          <t>오오샵 서구청점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>gosm06@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1398-9916</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
+          <t>인천광역시 서구 심곡로 44-1 108호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailhee_</t>
+          <t>https://www.instagram.com/55shop_simgock</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4211,13 +4255,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>343</v>
+        <v>136</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R41" t="n">
-        <v>358</v>
+        <v>148</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4226,17 +4270,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1280546741</t>
+          <t>1488480006</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280546741</t>
+          <t>https://m.place.naver.com/place/1488480006</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4248,29 +4292,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아트스타일네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>gotitkorea@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1418-1574</t>
+          <t>0507-1346-5358</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 30 416호</t>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
+          <t>https://www.instagram.com/nail.grimmy</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4305,13 +4349,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>116</v>
+        <v>349</v>
       </c>
       <c r="Q42" t="n">
-        <v>291</v>
+        <v>54</v>
       </c>
       <c r="R42" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4320,17 +4364,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1976908458</t>
+          <t>1125220368</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976908458</t>
+          <t>https://m.place.naver.com/place/1125220368</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4342,29 +4386,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>루비네일</t>
+          <t>네일드벨라 인천검단점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ruby1004_mj@naver.com</t>
+          <t>naildebella@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1486-3019</t>
+          <t>0507-1356-3442</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
+          <t>인천광역시 서구 이음대로 384 307호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rubynail3006</t>
+          <t>https://blog.naver.com/naildebella</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4379,7 +4423,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4399,13 +4443,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="Q43" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="R43" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4414,17 +4458,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1233475580</t>
+          <t>1219318994</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233475580</t>
+          <t>https://m.place.naver.com/place/1219318994</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4436,25 +4480,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>이르미네일</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>블링뷰네일</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bv_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1391-3129</t>
+          <t>0507-1350-9502</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ezxgrG</t>
+          <t>http://pf.kakao.com/_RqUxcG</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4489,13 +4537,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>234</v>
+        <v>118</v>
       </c>
       <c r="Q44" t="n">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="R44" t="n">
-        <v>341</v>
+        <v>271</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4504,17 +4552,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1596414337</t>
+          <t>1259415075</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596414337</t>
+          <t>https://m.place.naver.com/place/1259415075</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4526,29 +4574,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뉴아네일</t>
+          <t>라나뷰티 청라본점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>wlsdl2102@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1336-2796</t>
+          <t>0507-1392-1325</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 418 101호</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newa_nail25</t>
+          <t>https://www.instagram.com/_rananail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4574,7 +4622,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4583,13 +4631,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>88</v>
+        <v>460</v>
       </c>
       <c r="Q45" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="R45" t="n">
-        <v>213</v>
+        <v>485</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4598,17 +4646,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1799034051</t>
+          <t>1071013615</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799034051</t>
+          <t>https://m.place.naver.com/place/1071013615</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4620,29 +4668,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>제이제이네일</t>
+          <t>손끝한올네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>foiri@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1319-1270</t>
+          <t>0507-1392-5639</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
+          <t>인천광역시 서구 바리미로 17 2층 203호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jj__nail___</t>
+          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4677,13 +4725,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="R46" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4692,17 +4740,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2011413114</t>
+          <t>2013624857</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011413114</t>
+          <t>https://m.place.naver.com/place/2013624857</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4714,30 +4762,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>루비네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ruby1004_mj@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1486-3019</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>https://www.instagram.com/rubynail3006</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4758,7 +4810,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4767,13 +4819,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>349</v>
+        <v>280</v>
       </c>
       <c r="Q47" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="R47" t="n">
-        <v>426</v>
+        <v>343</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4782,17 +4834,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>1233475580</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/1233475580</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4804,29 +4856,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일도빛나</t>
+          <t>네일드림</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sjh888347@naver.com</t>
+          <t>shsally0122@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1302-9518</t>
+          <t>0507-1335-1809</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 551 동곡프라자 1층 107호</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_bitna</t>
+          <t>http://instagram.com/naild_lim</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4861,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>477</v>
+        <v>356</v>
       </c>
       <c r="Q48" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="R48" t="n">
-        <v>572</v>
+        <v>364</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4876,17 +4928,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1239607974</t>
+          <t>1192065742</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239607974</t>
+          <t>https://m.place.naver.com/place/1192065742</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4898,29 +4950,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>포네하네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>forestnh@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1400-8523</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://blog.naver.com/forestnh</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4955,13 +5007,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>615</v>
+        <v>337</v>
       </c>
       <c r="Q49" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="R49" t="n">
-        <v>746</v>
+        <v>453</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4970,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1672609930</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1672609930</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4992,29 +5044,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>네일디핀</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>sina1310@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1346-5358</t>
+          <t>0507-1476-4029</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.grimmy</t>
+          <t>https://www.instagram.com/naildeepin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5049,13 +5101,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>349</v>
+        <v>88</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
-        <v>403</v>
+        <v>95</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5064,17 +5116,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1125220368</t>
+          <t>2047454568</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125220368</t>
+          <t>https://m.place.naver.com/place/2047454568</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5086,30 +5138,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일에딧</t>
+          <t>뉴아네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>byddooroo@naver.com</t>
+          <t>kikiki_k@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1336-2796</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
+          <t>인천광역시 서구 승학로 418 101호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dZxhxcn</t>
+          <t>https://www.instagram.com/newa_nail25</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5130,7 +5186,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5139,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>781</v>
+        <v>89</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="R51" t="n">
-        <v>787</v>
+        <v>217</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5154,17 +5210,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2041818773</t>
+          <t>1799034051</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041818773</t>
+          <t>https://m.place.naver.com/place/1799034051</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5176,30 +5232,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에스영이네일</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>소요뷰티</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>raindrop3113@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1322-9488</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
+          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JAxdFs</t>
+          <t>https://www.instagram.com/soyo._.beauty</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5220,7 +5276,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5229,13 +5285,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>426</v>
+        <v>576</v>
       </c>
       <c r="Q52" t="n">
-        <v>188</v>
+        <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>614</v>
+        <v>581</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5244,17 +5300,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1726483094</t>
+          <t>1142806255</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726483094</t>
+          <t>https://m.place.naver.com/place/1142806255</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5266,34 +5322,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>라나뷰티 청라본점</t>
+          <t>네일벨</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>nailbelle@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1392-1325</t>
+          <t>0507-1324-7499</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+          <t>인천광역시 서구 원창로229번길 39 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_rananail</t>
+          <t>http://pf.kakao.com/_Nmwmxb</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5323,13 +5379,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>459</v>
+        <v>139</v>
       </c>
       <c r="Q53" t="n">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="R53" t="n">
-        <v>484</v>
+        <v>354</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5338,17 +5394,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1071013615</t>
+          <t>1895861710</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071013615</t>
+          <t>https://m.place.naver.com/place/1895861710</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5360,29 +5416,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>라라뷰티</t>
+          <t>풋라인 / 발각질 무좀발톱 손톱 내성발톱</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>rmatnr0203@naver.com</t>
+          <t>footline_@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1446-6698</t>
+          <t>0507-1413-5896</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 481 301호</t>
+          <t>인천광역시 서구 서곶로 50 3동 2층 B226호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__lalabeauty__</t>
+          <t>https://blog.naver.com/footline_</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5397,7 +5453,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5413,17 +5469,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>632</v>
+        <v>92</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R54" t="n">
-        <v>671</v>
+        <v>132</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5432,17 +5488,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1220420271</t>
+          <t>1082466960</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220420271</t>
+          <t>https://m.place.naver.com/place/1082466960</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5454,29 +5510,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>맑은네일&amp;오로지푸스 인천검단신도시점</t>
+          <t>네일달다 청라점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ekal5027@naver.com</t>
+          <t>haru_log_in@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1318-8700</t>
+          <t>0507-1325-3255</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서로3로 50 모아미래도 엘리트파크 상가1동109호</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/malgunnail</t>
+          <t>http://instagram.com/naildalda_</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5511,13 +5567,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>418</v>
+        <v>622</v>
       </c>
       <c r="Q55" t="n">
-        <v>57</v>
+        <v>239</v>
       </c>
       <c r="R55" t="n">
-        <v>475</v>
+        <v>861</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5526,17 +5582,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1926633328</t>
+          <t>1040857451</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926633328</t>
+          <t>https://m.place.naver.com/place/1040857451</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5548,29 +5604,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일갱 인천검단점</t>
+          <t>레푸스 청라점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>nailgang_@naver.com</t>
+          <t>dldeoqkr@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1353-4100</t>
+          <t>0507-1337-0812</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bJxdCG</t>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5605,13 +5661,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1696</v>
+        <v>301</v>
       </c>
       <c r="Q56" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="R56" t="n">
-        <v>1727</v>
+        <v>369</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5620,17 +5676,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1098311831</t>
+          <t>1742485791</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098311831</t>
+          <t>https://m.place.naver.com/place/1742485791</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5642,34 +5698,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>오늘의기분 네일 청라본점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>bae_tamine@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>0507-1307-8929</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>http://pf.kakao.com/_pxcsgb</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5679,7 +5735,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5690,7 +5746,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5699,13 +5755,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>567</v>
+        <v>353</v>
       </c>
       <c r="Q57" t="n">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="R57" t="n">
-        <v>700</v>
+        <v>430</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5714,17 +5770,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>1747055394</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/1747055394</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5736,29 +5792,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>오오샵 검단점</t>
+          <t>미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>dhaldud10@naver.com</t>
+          <t>mielnailbrow@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>070-4062-0556</t>
+          <t>0507-1355-4026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 159 1층 105호</t>
+          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop/</t>
+          <t>https://www.instagram.com/mielnailbrow_</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5793,13 +5849,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>621</v>
+        <v>731</v>
       </c>
       <c r="Q58" t="n">
-        <v>25</v>
+        <v>401</v>
       </c>
       <c r="R58" t="n">
-        <v>646</v>
+        <v>1132</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5808,17 +5864,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1739642099</t>
+          <t>409746804</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739642099</t>
+          <t>https://m.place.naver.com/place/409746804</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5830,29 +5886,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>레푸스검단점&amp;로브</t>
+          <t>네일소소</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>refussgumdan@naver.com</t>
+          <t>rkswlwoddl84@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1345-7844</t>
+          <t>0507-1415-2417</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
+          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_gumdan</t>
+          <t>https://www.instagram.com/nail_so_so</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5887,13 +5943,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>511</v>
+        <v>271</v>
       </c>
       <c r="Q59" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="R59" t="n">
-        <v>661</v>
+        <v>291</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5902,17 +5958,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1967477084</t>
+          <t>1394957062</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967477084</t>
+          <t>https://m.place.naver.com/place/1394957062</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5924,29 +5980,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일디핀</t>
+          <t>네일무디크</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sina1310@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1476-4029</t>
+          <t>0507-1375-3428</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildeepin</t>
+          <t>https://www.instagram.com/nail_moodique</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5981,13 +6037,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R60" t="n">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5996,17 +6052,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2047454568</t>
+          <t>1811715033</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047454568</t>
+          <t>https://m.place.naver.com/place/1811715033</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6018,29 +6074,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>인생네일 청라본점</t>
+          <t>단감네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>askflclsrna@naver.com</t>
+          <t>sytf170@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1301-5228</t>
+          <t>0507-1374-8432</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/life_nail_salon</t>
+          <t>https://www.instagram.com/dangam_nail/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6075,13 +6131,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>337</v>
       </c>
       <c r="R61" t="n">
-        <v>361</v>
+        <v>544</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6090,17 +6146,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1764464663</t>
+          <t>1985862694</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764464663</t>
+          <t>https://m.place.naver.com/place/1985862694</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6112,29 +6168,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일을기억해</t>
+          <t>아이퀸네일 청라점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>rimo0904@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1491-7279</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/remember._nails</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6160,7 +6216,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6169,13 +6225,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>210</v>
+        <v>314</v>
       </c>
       <c r="Q62" t="n">
-        <v>44</v>
+        <v>270</v>
       </c>
       <c r="R62" t="n">
-        <v>254</v>
+        <v>584</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6184,17 +6240,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1811328950</t>
+          <t>1330577008</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811328950</t>
+          <t>https://m.place.naver.com/place/1330577008</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6206,29 +6262,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>다린네일</t>
+          <t>레푸스검단점&amp;로브</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>merry0903_@naver.com</t>
+          <t>refussgumdan@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1419-3567</t>
+          <t>0507-1345-7844</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한중로 10 메르시타워 501호(1층 메가커피건물5층)</t>
+          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/DARIN.GLOBAL</t>
+          <t>https://www.instagram.com/refuss_gumdan</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6263,13 +6319,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>212</v>
+        <v>513</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="R63" t="n">
-        <v>224</v>
+        <v>663</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6278,17 +6334,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1665621156</t>
+          <t>1967477084</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1665621156</t>
+          <t>https://m.place.naver.com/place/1967477084</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6300,25 +6356,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일하고가람</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>네일클로버</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1468-0177</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailharam_</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6353,13 +6413,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="R64" t="n">
-        <v>126</v>
+        <v>221</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6368,17 +6428,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1958882228</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958882228</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6390,25 +6450,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>단감네일</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>와우뷰티 청라점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>e5174@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1374-8432</t>
+          <t>0507-1323-1043</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dangam_nail/</t>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6443,13 +6507,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>205</v>
+        <v>92</v>
       </c>
       <c r="Q65" t="n">
-        <v>337</v>
+        <v>49</v>
       </c>
       <c r="R65" t="n">
-        <v>542</v>
+        <v>141</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6458,17 +6522,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1985862694</t>
+          <t>1012993987</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985862694</t>
+          <t>https://m.place.naver.com/place/1012993987</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6480,29 +6544,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>오늘도네일도</t>
+          <t>아젤리아네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nail_oneul@naver.com</t>
+          <t>dlwlgus0914@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1449-7506</t>
+          <t>0507-1491-3901</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_oneul</t>
+          <t>https://blog.naver.com/dlwlgus0914</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6537,13 +6601,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>813</v>
+        <v>132</v>
       </c>
       <c r="Q66" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="R66" t="n">
-        <v>855</v>
+        <v>145</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6552,17 +6616,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1810678383</t>
+          <t>1393226062</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810678383</t>
+          <t>https://m.place.naver.com/place/1393226062</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6574,34 +6638,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일벨</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nailbelle@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1324-7499</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원창로229번길 39 1층</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Nmwmxb</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6611,7 +6675,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6622,22 +6686,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>139</v>
+        <v>907</v>
       </c>
       <c r="Q67" t="n">
-        <v>215</v>
+        <v>380</v>
       </c>
       <c r="R67" t="n">
-        <v>354</v>
+        <v>1287</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6646,17 +6710,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1895861710</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895861710</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6668,25 +6732,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>무드온네일</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>네일,사계절</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>siryyam@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1494-6716</t>
+          <t>0507-1360-4822</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
+          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moodon.nail</t>
+          <t>https://www.instagram.com/nail_4season</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6721,13 +6789,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>49</v>
+        <v>369</v>
       </c>
       <c r="Q68" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R68" t="n">
-        <v>62</v>
+        <v>377</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6736,17 +6804,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2044601280</t>
+          <t>1216076936</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044601280</t>
+          <t>https://m.place.naver.com/place/1216076936</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6758,29 +6826,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일달다 청라점</t>
+          <t>루미온네일 검단신도시점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>haru_log_in@naver.com</t>
+          <t>rowawoo@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1325-3255</t>
+          <t>0507-1347-5944</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildalda_</t>
+          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6815,13 +6883,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>622</v>
+        <v>42</v>
       </c>
       <c r="Q69" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>861</v>
+        <v>50</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6830,17 +6898,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1040857451</t>
+          <t>2012993603</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040857451</t>
+          <t>https://m.place.naver.com/place/2012993603</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6852,34 +6920,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>해온네일</t>
+          <t>하프네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>cocory_snb@naver.com</t>
+          <t>half7571@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1368-2279</t>
+          <t>0507-1380-7571</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
+          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
+          <t>https://www.instagram.com/half_nail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6889,7 +6957,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6905,17 +6973,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>50</v>
+        <v>1613</v>
       </c>
       <c r="Q70" t="n">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="R70" t="n">
-        <v>67</v>
+        <v>1804</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6924,17 +6992,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2095874863</t>
+          <t>1259862588</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095874863</t>
+          <t>https://m.place.naver.com/place/1259862588</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6946,25 +7014,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일,사계절</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dlgufl0924@naver.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1360-4822</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_4season</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6999,13 +7071,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>369</v>
+        <v>610</v>
       </c>
       <c r="Q71" t="n">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="R71" t="n">
-        <v>377</v>
+        <v>828</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7014,17 +7086,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1216076936</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216076936</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7036,25 +7108,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>와우뷰티 청라점</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>감성네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>gamseongnail@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1323-1043</t>
+          <t>0507-1424-4545</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/gam_seongnail/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7089,13 +7165,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>91</v>
+        <v>449</v>
       </c>
       <c r="Q72" t="n">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="R72" t="n">
-        <v>140</v>
+        <v>614</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7104,17 +7180,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1012993987</t>
+          <t>1382824710</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012993987</t>
+          <t>https://m.place.naver.com/place/1382824710</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7126,25 +7202,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일델루나</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>네일또온나 청라점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2xmania2xj@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1358-7017</t>
+          <t>0507-1338-3150</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_delluna</t>
+          <t>https://www.instagram.com/nail_tto_onna</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7179,13 +7259,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1528</v>
+        <v>247</v>
       </c>
       <c r="Q73" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="R73" t="n">
-        <v>1543</v>
+        <v>310</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7194,17 +7274,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1852644091</t>
+          <t>1546215593</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852644091</t>
+          <t>https://m.place.naver.com/place/1546215593</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7216,30 +7296,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>네일도속눈썹</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>naildorash1@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1395-6008</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 서구 염곡로 346-1 1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>http://instagram.com/naildo_lash</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7249,7 +7333,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7260,7 +7344,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7269,13 +7353,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Q74" t="n">
-        <v>40</v>
+        <v>289</v>
       </c>
       <c r="R74" t="n">
-        <v>446</v>
+        <v>693</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7284,17 +7368,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1958392738</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1958392738</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7306,31 +7390,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>도르네일</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>젤로미네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>nailjellomi@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+          <t>인천광역시 서구 검단로 480 3층 305호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/hCmFKNexK</t>
+          <t>https://www.instagram.com/nail._.jellomi</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7355,13 +7443,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>722</v>
+        <v>91</v>
       </c>
       <c r="Q75" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="R75" t="n">
-        <v>775</v>
+        <v>140</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7370,17 +7458,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1001824596</t>
+          <t>2051638884</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001824596</t>
+          <t>https://m.place.naver.com/place/2051638884</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7392,34 +7480,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>블링뷰네일</t>
+          <t>해온네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bv_nail@naver.com</t>
+          <t>cocory_snb@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1350-9502</t>
+          <t>0507-1368-2279</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RqUxcG</t>
+          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7440,22 +7528,22 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="Q76" t="n">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="R76" t="n">
-        <v>270</v>
+        <v>71</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7464,17 +7552,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1259415075</t>
+          <t>2095874863</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259415075</t>
+          <t>https://m.place.naver.com/place/2095874863</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/서구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서구_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mm9208291@naver.com</t>
+          <t>yulee410@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1030,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인생네일 청라본점</t>
+          <t>네일도빛나</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>askflclsrna@naver.com</t>
+          <t>sjh888347@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1301-5228</t>
+          <t>0507-1302-9518</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+          <t>인천광역시 서구 승학로 551 동곡프라자 1층 107호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/life_nail_salon</t>
+          <t>https://www.instagram.com/naildo_bitna</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>351</v>
+        <v>477</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="R7" t="n">
-        <v>362</v>
+        <v>572</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1764464663</t>
+          <t>1239607974</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764464663</t>
+          <t>https://m.place.naver.com/place/1239607974</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
+          <t>인생네일 청라본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mina20624@naver.com</t>
+          <t>askflclsrna@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1332-6316</t>
+          <t>0507-1301-5228</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>https://www.instagram.com/life_nail_salon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>665</v>
+        <v>351</v>
       </c>
       <c r="Q8" t="n">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="R8" t="n">
-        <v>832</v>
+        <v>362</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>1764464663</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/1764464663</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>제이언니네 청라본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>mina20624@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1332-6316</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>620</v>
+        <v>665</v>
       </c>
       <c r="Q9" t="n">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="R9" t="n">
-        <v>751</v>
+        <v>832</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일희 검단신도시점</t>
+          <t>섬세하나네일 청라본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gosm06@naver.com</t>
+          <t>sumsehana@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1398-9916</t>
+          <t>0507-1481-0788</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailhee_</t>
+          <t>https://blog.naver.com/sumsehana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>344</v>
+        <v>620</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="R10" t="n">
-        <v>359</v>
+        <v>751</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1280546741</t>
+          <t>1251340543</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280546741</t>
+          <t>https://m.place.naver.com/place/1251340543</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,35 +1406,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>달미네일</t>
+          <t>네일희 검단신도시점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jinjoo8570@naver.com</t>
+          <t>gosm06@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1398-9916</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
+          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/aWKRY9YJt</t>
+          <t>https://www.instagram.com/_nailhee_</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>203</v>
+        <v>344</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
-        <v>213</v>
+        <v>359</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2000818117</t>
+          <t>1280546741</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000818117</t>
+          <t>https://m.place.naver.com/place/1280546741</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,39 +1500,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아트스타일네일</t>
+          <t>달미네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gotitkorea@naver.com</t>
+          <t>jinjoo8570@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1418-1574</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 30 416호</t>
+          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
+          <t>https://toss.place/_lb/aWKRY9YJt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="Q12" t="n">
-        <v>295</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>412</v>
+        <v>214</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1976908458</t>
+          <t>2000818117</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976908458</t>
+          <t>https://m.place.naver.com/place/2000818117</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>무드온네일</t>
+          <t>아트스타일네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>llggggll@naver.com</t>
+          <t>gotitkorea@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1494-6716</t>
+          <t>0507-1418-1574</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
+          <t>인천광역시 서구 염곡로464번길 30 416호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moodon.nail</t>
+          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>296</v>
       </c>
       <c r="R13" t="n">
-        <v>68</v>
+        <v>413</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2044601280</t>
+          <t>1976908458</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044601280</t>
+          <t>https://m.place.naver.com/place/1976908458</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1684,29 +1684,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>무드온네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>llggggll@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>0507-1494-6716</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>https://www.instagram.com/moodon.nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>567</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="n">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>700</v>
+        <v>68</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>2044601280</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/2044601280</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1778,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>오오샵 검단점</t>
+          <t>프롬쥬네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dhaldud10@naver.com</t>
+          <t>dlaalswn89@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>070-4062-0556</t>
+          <t>0507-1327-0666</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 159 1층 105호</t>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop/</t>
+          <t>https://blog.naver.com/dlaalswn89</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>622</v>
+        <v>567</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="R15" t="n">
-        <v>647</v>
+        <v>700</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1739642099</t>
+          <t>1545913000</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739642099</t>
+          <t>https://m.place.naver.com/place/1545913000</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일델루나</t>
+          <t>오오샵 검단점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>eatingzzz@naver.com</t>
+          <t>dhaldud10@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1358-7017</t>
+          <t>070-4062-0556</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+          <t>인천광역시 서구 완정로 159 1층 105호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_delluna</t>
+          <t>https://www.instagram.com/55_allinone_shop/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1534</v>
+        <v>623</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R16" t="n">
-        <v>1549</v>
+        <v>648</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1852644091</t>
+          <t>1739642099</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852644091</t>
+          <t>https://m.place.naver.com/place/1739642099</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1966,29 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>루안네일 토탈뷰티 검단점</t>
+          <t>네일델루나</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>luannail@naver.com</t>
+          <t>eatingzzz@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1349-7727</t>
+          <t>0507-1358-7017</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 단봉로 97-7 1층 112호</t>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://http//pf.kakao.com/_vALxgG</t>
+          <t>http://instagram.com/nail_delluna</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2014,7 +2014,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>742</v>
+        <v>1534</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
-        <v>745</v>
+        <v>1549</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1840082670</t>
+          <t>1852644091</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840082670</t>
+          <t>https://m.place.naver.com/place/1852644091</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2060,25 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>카밀라네일 검단신도시점</t>
+          <t>루안네일 토탈뷰티 검단점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ojolfkj@naver.com</t>
+          <t>luannail@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1349-7727</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
+          <t>인천광역시 서구 단봉로 97-7 1층 112호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
+          <t>https://http//pf.kakao.com/_vALxgG</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2104,7 +2108,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2113,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>759</v>
+        <v>742</v>
       </c>
       <c r="Q18" t="n">
-        <v>369</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1128</v>
+        <v>745</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,12 +2132,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1490697723</t>
+          <t>1840082670</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490697723</t>
+          <t>https://m.place.naver.com/place/1840082670</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2150,29 +2154,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>맑은네일&amp;오로지푸스 인천검단신도시점</t>
+          <t>카밀라네일 검단신도시점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ekal5027@naver.com</t>
+          <t>ojolfkj@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1318-8700</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서로3로 50 모아미래도 엘리트파크 상가1동109호</t>
+          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/malgunnail</t>
+          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>418</v>
+        <v>759</v>
       </c>
       <c r="Q19" t="n">
-        <v>60</v>
+        <v>369</v>
       </c>
       <c r="R19" t="n">
-        <v>478</v>
+        <v>1128</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1926633328</t>
+          <t>1490697723</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926633328</t>
+          <t>https://m.place.naver.com/place/1490697723</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2244,25 +2244,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일바연</t>
+          <t>루씨르네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yeerina@naver.com</t>
+          <t>lucirnail_@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1369-3734</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
+          <t>인천광역시 서구 가정로 390 1층 107호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.by.yeon</t>
+          <t>https://blog.naver.com/lucirnail_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2277,7 +2281,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2297,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>688</v>
+        <v>77</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="R20" t="n">
-        <v>713</v>
+        <v>225</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,12 +2316,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1017865788</t>
+          <t>1871859211</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017865788</t>
+          <t>https://m.place.naver.com/place/1871859211</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2334,29 +2338,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일위드유 문제성발톱 속눈썹</t>
+          <t>네일바연</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nail_with_yoo@naver.com</t>
+          <t>yeerina@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1344-1735</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_with_yoo</t>
+          <t>http://instagram.com/nail.by.yeon</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>259</v>
+        <v>688</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R21" t="n">
-        <v>288</v>
+        <v>713</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1776289071</t>
+          <t>1017865788</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776289071</t>
+          <t>https://m.place.naver.com/place/1017865788</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2428,30 +2428,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일에딧</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>byddooroo@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1344-1735</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dZxhxcn</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2472,7 +2476,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2481,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>801</v>
+        <v>259</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="R22" t="n">
-        <v>807</v>
+        <v>288</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2496,12 +2500,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2041818773</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041818773</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2518,34 +2522,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>네일에딧</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mobi04@naver.com</t>
+          <t>byddooroo@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1398-8291</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2566,7 +2566,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>573</v>
+        <v>801</v>
       </c>
       <c r="Q23" t="n">
-        <v>846</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>1419</v>
+        <v>807</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2612,29 +2612,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1248네일</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1248nail@naver.com</t>
+          <t>mobi04@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1479-8978</t>
+          <t>0507-1398-8291</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1248_nail</t>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>457</v>
+        <v>573</v>
       </c>
       <c r="Q24" t="n">
-        <v>267</v>
+        <v>846</v>
       </c>
       <c r="R24" t="n">
-        <v>724</v>
+        <v>1419</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1537239618</t>
+          <t>1090442730</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537239618</t>
+          <t>https://m.place.naver.com/place/1090442730</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2706,35 +2706,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>도르네일</t>
+          <t>1248네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bnm4818@naver.com</t>
+          <t>1248nail@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1479-8978</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/hCmFKNexK</t>
+          <t>https://www.instagram.com/1248_nail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2759,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>728</v>
+        <v>457</v>
       </c>
       <c r="Q25" t="n">
-        <v>54</v>
+        <v>267</v>
       </c>
       <c r="R25" t="n">
-        <v>782</v>
+        <v>724</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2774,12 +2778,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1001824596</t>
+          <t>1537239618</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001824596</t>
+          <t>https://m.place.naver.com/place/1537239618</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2796,29 +2800,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>오늘도네일도</t>
+          <t>모하카 네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nail_oneul@naver.com</t>
+          <t>khss11550@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1449-7506</t>
+          <t>0507-1376-7909</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+          <t>인천광역시 서구 바리미로5번길 12 다승프라자 2차 602호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_oneul</t>
+          <t>https://www.instagram.com/nailmohaka</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2833,7 +2837,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2853,13 +2857,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>815</v>
+        <v>169</v>
       </c>
       <c r="Q26" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R26" t="n">
-        <v>857</v>
+        <v>202</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2868,12 +2872,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1810678383</t>
+          <t>1979256613</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810678383</t>
+          <t>https://m.place.naver.com/place/1979256613</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2890,29 +2894,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>악어네일&amp;속눈썹</t>
+          <t>도르네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bestone4848@naver.com</t>
+          <t>bnm4818@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1325-3157</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qxjdtG</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2938,7 +2938,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>308</v>
+        <v>728</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="R27" t="n">
-        <v>318</v>
+        <v>782</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1369177883</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369177883</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2984,29 +2984,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일이음 검단신도시점</t>
+          <t>오늘도네일도</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>slovejy@naver.com</t>
+          <t>nail_oneul@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1373-3055</t>
+          <t>0507-1449-7506</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailieum</t>
+          <t>https://blog.naver.com/nail_oneul</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3041,13 +3041,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1322</v>
+        <v>816</v>
       </c>
       <c r="Q28" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="R28" t="n">
-        <v>1394</v>
+        <v>858</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1729889261</t>
+          <t>1810678383</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729889261</t>
+          <t>https://m.place.naver.com/place/1810678383</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3078,34 +3078,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>어레브네일</t>
+          <t>악어네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>anwlro9344@naver.com</t>
+          <t>bestone4848@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1354-5482</t>
+          <t>0507-1325-3157</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
+          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anwlro9344</t>
+          <t>http://pf.kakao.com/_qxjdtG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3126,7 +3126,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>70</v>
+        <v>308</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R29" t="n">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1364434683</t>
+          <t>1369177883</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364434683</t>
+          <t>https://m.place.naver.com/place/1369177883</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3172,34 +3172,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>이루아네일</t>
+          <t>네일이음 검단신도시점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nec1153@naver.com</t>
+          <t>slovejy@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1373-3055</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>https://www.instagram.com/nailieum</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>136</v>
+        <v>1324</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="R30" t="n">
-        <v>158</v>
+        <v>1396</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1729889261</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1729889261</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3266,34 +3266,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>신스티니네일</t>
+          <t>어레브네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jin70826@naver.com</t>
+          <t>anwlro9344@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1399-4665</t>
+          <t>0507-1354-5482</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_tkuSxj</t>
+          <t>https://blog.naver.com/anwlro9344</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3314,7 +3314,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1137</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="n">
-        <v>845</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>1982</v>
+        <v>75</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1503407402</t>
+          <t>1364434683</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503407402</t>
+          <t>https://m.place.naver.com/place/1364434683</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3360,29 +3360,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>이르미네일</t>
+          <t>이루아네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>aboutdanchuu@naver.com</t>
+          <t>nec1153@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1391-3129</t>
+          <t>0507-1400-0973</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ezxgrG</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3408,7 +3408,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="Q32" t="n">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
-        <v>342</v>
+        <v>158</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1596414337</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596414337</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3454,34 +3454,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일무우 인천검단점</t>
+          <t>신스티니네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>n_mou@naver.com</t>
+          <t>jin70826@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1382-9824</t>
+          <t>0507-1399-4665</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
+          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/n_mou</t>
+          <t>http://pf.kakao.com/_tkuSxj</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>327</v>
+        <v>1137</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>845</v>
       </c>
       <c r="R33" t="n">
-        <v>341</v>
+        <v>1982</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1965956470</t>
+          <t>1503407402</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965956470</t>
+          <t>https://m.place.naver.com/place/1503407402</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3548,34 +3548,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일하롱</t>
+          <t>이르미네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mimmmm95_@naver.com</t>
+          <t>aboutdanchuu@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1438-1442</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.harong</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3596,7 +3596,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3605,13 +3605,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>536</v>
+        <v>234</v>
       </c>
       <c r="Q34" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="R34" t="n">
-        <v>572</v>
+        <v>342</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1264211104</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264211104</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3642,29 +3642,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
+          <t>네일무우 인천검단점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dodofamily_mam@naver.com</t>
+          <t>n_mou@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1382-9824</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>https://blog.naver.com/n_mou</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3699,13 +3699,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>406</v>
+        <v>327</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="R35" t="n">
-        <v>446</v>
+        <v>341</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1965956470</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1965956470</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3736,29 +3736,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>소담뷰티 검단신도시점</t>
+          <t>네일하롱</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>on323652@naver.com</t>
+          <t>mimmmm95_@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1484-9220</t>
+          <t>0507-1438-1442</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sodam_beauty1</t>
+          <t>https://www.instagram.com/nail._.harong</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>219</v>
+        <v>536</v>
       </c>
       <c r="Q36" t="n">
-        <v>326</v>
+        <v>36</v>
       </c>
       <c r="R36" t="n">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1342897161</t>
+          <t>1264211104</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342897161</t>
+          <t>https://m.place.naver.com/place/1264211104</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3830,29 +3830,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>바리에라네일</t>
+          <t>소담뷰티 검단신도시점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>rosekim1102@naver.com</t>
+          <t>on323652@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1390-9307</t>
+          <t>0507-1484-9220</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 8 409호</t>
+          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/varier_la_nail</t>
+          <t>https://www.instagram.com/sodam_beauty1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>327</v>
       </c>
       <c r="R37" t="n">
-        <v>211</v>
+        <v>546</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2090298265</t>
+          <t>1342897161</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090298265</t>
+          <t>https://m.place.naver.com/place/1342897161</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3924,34 +3924,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일갱 인천검단점</t>
+          <t>바리에라네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nailgang_@naver.com</t>
+          <t>rosekim1102@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1353-4100</t>
+          <t>0507-1390-9307</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
+          <t>인천광역시 서구 바리미로5번길 8 409호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bJxdCG</t>
+          <t>https://www.instagram.com/varier_la_nail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3972,7 +3972,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3981,13 +3981,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1700</v>
+        <v>172</v>
       </c>
       <c r="Q38" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R38" t="n">
-        <v>1731</v>
+        <v>211</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1098311831</t>
+          <t>2090298265</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098311831</t>
+          <t>https://m.place.naver.com/place/2090298265</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4018,30 +4018,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일인유</t>
+          <t>네일갱 인천검단점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bonheur0118@naver.com</t>
+          <t>nailgang_@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1353-4100</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
+          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inyou</t>
+          <t>http://pf.kakao.com/_bJxdCG</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4062,7 +4066,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4071,13 +4075,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1186</v>
+        <v>1700</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="R39" t="n">
-        <v>1201</v>
+        <v>1731</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,12 +4090,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1117254073</t>
+          <t>1098311831</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117254073</t>
+          <t>https://m.place.naver.com/place/1098311831</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4108,29 +4112,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>온다네일룸</t>
+          <t>네일인유</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dl7246@naver.com</t>
+          <t>bonheur0118@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1369-7246</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 179 3층</t>
+          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onda_nail_room/</t>
+          <t>https://www.instagram.com/nail_inyou</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>755</v>
+        <v>1186</v>
       </c>
       <c r="Q40" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="R40" t="n">
-        <v>801</v>
+        <v>1201</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1656364709</t>
+          <t>1117254073</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656364709</t>
+          <t>https://m.place.naver.com/place/1117254073</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4202,25 +4202,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>오오샵 서구청점</t>
+          <t>온다네일룸</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>dl7246@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1369-7246</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 심곡로 44-1 108호</t>
+          <t>인천광역시 서구 완정로 179 3층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55shop_simgock</t>
+          <t>https://www.instagram.com/onda_nail_room/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4255,13 +4259,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>136</v>
+        <v>755</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="R41" t="n">
-        <v>148</v>
+        <v>801</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,12 +4274,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1488480006</t>
+          <t>1656364709</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488480006</t>
+          <t>https://m.place.naver.com/place/1656364709</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4292,29 +4296,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>오오샵 서구청점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1346-5358</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+          <t>인천광역시 서구 심곡로 44-1 108호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.grimmy</t>
+          <t>https://www.instagram.com/55shop_simgock</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4349,13 +4349,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>349</v>
+        <v>136</v>
       </c>
       <c r="Q42" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="R42" t="n">
-        <v>403</v>
+        <v>148</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1125220368</t>
+          <t>1488480006</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125220368</t>
+          <t>https://m.place.naver.com/place/1488480006</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4480,34 +4480,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>블링뷰네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>bv_nail@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1350-9502</t>
+          <t>0507-1346-5358</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RqUxcG</t>
+          <t>https://www.instagram.com/nail.grimmy</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4537,13 +4537,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>118</v>
+        <v>349</v>
       </c>
       <c r="Q44" t="n">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="R44" t="n">
-        <v>271</v>
+        <v>403</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,12 +4552,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1259415075</t>
+          <t>1125220368</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259415075</t>
+          <t>https://m.place.naver.com/place/1125220368</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4574,34 +4574,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>라나뷰티 청라본점</t>
+          <t>블링뷰네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>bv_nail@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1392-1325</t>
+          <t>0507-1350-9502</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_rananail</t>
+          <t>http://pf.kakao.com/_RqUxcG</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>460</v>
+        <v>118</v>
       </c>
       <c r="Q45" t="n">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="R45" t="n">
-        <v>485</v>
+        <v>271</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1071013615</t>
+          <t>1259415075</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071013615</t>
+          <t>https://m.place.naver.com/place/1259415075</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4668,29 +4668,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>손끝한올네일</t>
+          <t>라나뷰티 청라본점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>foiri@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1392-5639</t>
+          <t>0507-1392-1325</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로 17 2층 203호</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
+          <t>https://www.instagram.com/_rananail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4716,7 +4716,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4725,13 +4725,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>77</v>
+        <v>460</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R46" t="n">
-        <v>95</v>
+        <v>485</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2013624857</t>
+          <t>1071013615</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013624857</t>
+          <t>https://m.place.naver.com/place/1071013615</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4762,29 +4762,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>루비네일</t>
+          <t>손끝한올네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ruby1004_mj@naver.com</t>
+          <t>foiri@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1486-3019</t>
+          <t>0507-1392-5639</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
+          <t>인천광역시 서구 바리미로 17 2층 203호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rubynail3006</t>
+          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="Q47" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="R47" t="n">
-        <v>343</v>
+        <v>95</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,12 +4834,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1233475580</t>
+          <t>2013624857</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233475580</t>
+          <t>https://m.place.naver.com/place/2013624857</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4856,29 +4856,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일드림</t>
+          <t>루비네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>shsally0122@naver.com</t>
+          <t>ruby1004_mj@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1335-1809</t>
+          <t>0507-1486-3019</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
+          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://instagram.com/naild_lim</t>
+          <t>https://www.instagram.com/rubynail3006</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4913,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="R48" t="n">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,12 +4928,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1192065742</t>
+          <t>1233475580</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192065742</t>
+          <t>https://m.place.naver.com/place/1233475580</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4950,29 +4950,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>네일드림</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>shsally0122@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1335-1809</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>http://instagram.com/naild_lim</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="Q49" t="n">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="R49" t="n">
-        <v>453</v>
+        <v>364</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,12 +5022,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1192065742</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1192065742</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5044,29 +5044,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일디핀</t>
+          <t>포네하네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sina1310@naver.com</t>
+          <t>forestnh@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1476-4029</t>
+          <t>0507-1400-8523</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildeepin</t>
+          <t>https://blog.naver.com/forestnh</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>88</v>
+        <v>337</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="R50" t="n">
-        <v>95</v>
+        <v>453</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2047454568</t>
+          <t>1672609930</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047454568</t>
+          <t>https://m.place.naver.com/place/1672609930</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5138,29 +5138,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>뉴아네일</t>
+          <t>네일디핀</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kikiki_k@naver.com</t>
+          <t>sina1310@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1336-2796</t>
+          <t>0507-1476-4029</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 418 101호</t>
+          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newa_nail25</t>
+          <t>https://www.instagram.com/naildeepin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5198,10 +5198,10 @@
         <v>89</v>
       </c>
       <c r="Q51" t="n">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="R51" t="n">
-        <v>217</v>
+        <v>96</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1799034051</t>
+          <t>2047454568</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799034051</t>
+          <t>https://m.place.naver.com/place/2047454568</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5232,25 +5232,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>소요뷰티</t>
+          <t>뉴아네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>raindrop3113@naver.com</t>
+          <t>kikiki_k@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1336-2796</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
+          <t>인천광역시 서구 승학로 418 101호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soyo._.beauty</t>
+          <t>https://www.instagram.com/newa_nail25</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5285,13 +5289,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>576</v>
+        <v>89</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="R52" t="n">
-        <v>581</v>
+        <v>217</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5300,12 +5304,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1142806255</t>
+          <t>1799034051</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142806255</t>
+          <t>https://m.place.naver.com/place/1799034051</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5322,34 +5326,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일벨</t>
+          <t>소요뷰티</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nailbelle@naver.com</t>
+          <t>raindrop3113@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1324-7499</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원창로229번길 39 1층</t>
+          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Nmwmxb</t>
+          <t>https://www.instagram.com/soyo._.beauty</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5370,7 +5370,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5379,13 +5379,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>139</v>
+        <v>577</v>
       </c>
       <c r="Q53" t="n">
-        <v>215</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>354</v>
+        <v>582</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1895861710</t>
+          <t>1142806255</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895861710</t>
+          <t>https://m.place.naver.com/place/1142806255</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5416,34 +5416,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>풋라인 / 발각질 무좀발톱 손톱 내성발톱</t>
+          <t>네일벨</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>footline_@naver.com</t>
+          <t>nailbelle@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1413-5896</t>
+          <t>0507-1324-7499</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 50 3동 2층 B226호</t>
+          <t>인천광역시 서구 원창로229번길 39 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/footline_</t>
+          <t>http://pf.kakao.com/_Nmwmxb</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5464,22 +5464,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="R54" t="n">
-        <v>132</v>
+        <v>354</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1082466960</t>
+          <t>1895861710</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1082466960</t>
+          <t>https://m.place.naver.com/place/1895861710</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5510,29 +5510,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일달다 청라점</t>
+          <t>풋라인 / 발각질 무좀발톱 손톱 내성발톱</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>haru_log_in@naver.com</t>
+          <t>footline_@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1325-3255</t>
+          <t>0507-1413-5896</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+          <t>인천광역시 서구 서곶로 50 3동 2층 B226호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildalda_</t>
+          <t>https://blog.naver.com/footline_</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>622</v>
+        <v>93</v>
       </c>
       <c r="Q55" t="n">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="R55" t="n">
-        <v>861</v>
+        <v>133</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,12 +5582,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1040857451</t>
+          <t>1082466960</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040857451</t>
+          <t>https://m.place.naver.com/place/1082466960</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5604,34 +5604,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>레푸스 청라점</t>
+          <t>네일달다 청라점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>dldeoqkr@naver.com</t>
+          <t>haru_log_in@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1337-0812</t>
+          <t>0507-1325-3255</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYKKOFJe</t>
+          <t>http://instagram.com/naildalda_</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5652,7 +5652,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5661,13 +5661,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>301</v>
+        <v>622</v>
       </c>
       <c r="Q56" t="n">
-        <v>68</v>
+        <v>240</v>
       </c>
       <c r="R56" t="n">
-        <v>369</v>
+        <v>862</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1742485791</t>
+          <t>1040857451</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742485791</t>
+          <t>https://m.place.naver.com/place/1040857451</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5698,34 +5698,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
+          <t>레푸스 청라점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bae_tamine@naver.com</t>
+          <t>dldeoqkr@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1337-0812</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5755,13 +5755,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="Q57" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="R57" t="n">
-        <v>430</v>
+        <v>369</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>1742485791</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/1742485791</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5792,34 +5792,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>미엘네일브로우 인천가정점</t>
+          <t>오늘의기분 네일 청라본점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mielnailbrow@naver.com</t>
+          <t>bae_tamine@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1355-4026</t>
+          <t>0507-1307-8929</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mielnailbrow_</t>
+          <t>http://pf.kakao.com/_pxcsgb</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5840,7 +5840,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>731</v>
+        <v>353</v>
       </c>
       <c r="Q58" t="n">
-        <v>401</v>
+        <v>77</v>
       </c>
       <c r="R58" t="n">
-        <v>1132</v>
+        <v>430</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>409746804</t>
+          <t>1747055394</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/409746804</t>
+          <t>https://m.place.naver.com/place/1747055394</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5886,29 +5886,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일소소</t>
+          <t>미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>rkswlwoddl84@naver.com</t>
+          <t>mielnailbrow@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1415-2417</t>
+          <t>0507-1355-4026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
+          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_so_so</t>
+          <t>https://www.instagram.com/mielnailbrow_</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>271</v>
+        <v>731</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="R59" t="n">
-        <v>291</v>
+        <v>1132</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1394957062</t>
+          <t>409746804</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394957062</t>
+          <t>https://m.place.naver.com/place/409746804</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5980,29 +5980,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일무디크</t>
+          <t>블링루원뷰티</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>ball_11058@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1375-3428</t>
+          <t>0507-1462-3543</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_moodique</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6033,17 +6033,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="Q60" t="n">
         <v>9</v>
       </c>
       <c r="R60" t="n">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6052,12 +6052,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1811715033</t>
+          <t>1323823289</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811715033</t>
+          <t>https://m.place.naver.com/place/1323823289</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6074,34 +6074,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>단감네일</t>
+          <t>에스영이네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sytf170@naver.com</t>
+          <t>s02nail@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1374-8432</t>
+          <t>0507-1322-9488</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dangam_nail/</t>
+          <t>http://pf.kakao.com/_JAxdFs</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6122,7 +6122,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>207</v>
+        <v>428</v>
       </c>
       <c r="Q61" t="n">
-        <v>337</v>
+        <v>188</v>
       </c>
       <c r="R61" t="n">
-        <v>544</v>
+        <v>616</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1985862694</t>
+          <t>1726483094</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985862694</t>
+          <t>https://m.place.naver.com/place/1726483094</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6168,29 +6168,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
+          <t>네일무디크</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gamejaki@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1375-3428</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>https://www.instagram.com/nail_moodique</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6225,13 +6225,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="Q62" t="n">
-        <v>270</v>
+        <v>9</v>
       </c>
       <c r="R62" t="n">
-        <v>584</v>
+        <v>177</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>1811715033</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/1811715033</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6262,29 +6262,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>레푸스검단점&amp;로브</t>
+          <t>단감네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>refussgumdan@naver.com</t>
+          <t>sytf170@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1345-7844</t>
+          <t>0507-1374-8432</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_gumdan</t>
+          <t>https://www.instagram.com/dangam_nail/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>513</v>
+        <v>207</v>
       </c>
       <c r="Q63" t="n">
-        <v>150</v>
+        <v>337</v>
       </c>
       <c r="R63" t="n">
-        <v>663</v>
+        <v>544</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6334,12 +6334,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1967477084</t>
+          <t>1985862694</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967477084</t>
+          <t>https://m.place.naver.com/place/1985862694</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6356,29 +6356,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>아이퀸네일 청라점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1309-5041</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>213</v>
+        <v>314</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>273</v>
       </c>
       <c r="R64" t="n">
-        <v>221</v>
+        <v>587</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1024146721</t>
+          <t>1330577008</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024146721</t>
+          <t>https://m.place.naver.com/place/1330577008</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6450,29 +6450,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>와우뷰티 청라점</t>
+          <t>레푸스검단점&amp;로브</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>refussgumdan@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1323-1043</t>
+          <t>0507-1345-7844</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/refuss_gumdan</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6507,13 +6507,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>92</v>
+        <v>513</v>
       </c>
       <c r="Q65" t="n">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="R65" t="n">
-        <v>141</v>
+        <v>663</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6522,12 +6522,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1012993987</t>
+          <t>1967477084</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012993987</t>
+          <t>https://m.place.naver.com/place/1967477084</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6544,29 +6544,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>아젤리아네일</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>dlwlgus0914@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1491-3901</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlwlgus0914</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6601,13 +6601,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="Q66" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R66" t="n">
-        <v>145</v>
+        <v>221</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6616,12 +6616,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1393226062</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1393226062</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6638,29 +6638,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+          <t>와우뷰티 청라점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01192291122@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1338-0068</t>
+          <t>0507-1323-1043</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/01192291122</t>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>907</v>
+        <v>92</v>
       </c>
       <c r="Q67" t="n">
-        <v>380</v>
+        <v>49</v>
       </c>
       <c r="R67" t="n">
-        <v>1287</v>
+        <v>141</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6710,12 +6710,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1868333219</t>
+          <t>1012993987</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868333219</t>
+          <t>https://m.place.naver.com/place/1012993987</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6732,29 +6732,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일,사계절</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>siryyam@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1360-4822</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_4season</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6785,17 +6785,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>369</v>
+        <v>907</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>380</v>
       </c>
       <c r="R68" t="n">
-        <v>377</v>
+        <v>1287</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1216076936</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216076936</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6826,29 +6826,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>루미온네일 검단신도시점</t>
+          <t>네일,사계절</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>rowawoo@naver.com</t>
+          <t>siryyam@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1347-5944</t>
+          <t>0507-1360-4822</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
+          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
+          <t>https://www.instagram.com/nail_4season</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6883,13 +6883,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>42</v>
+        <v>369</v>
       </c>
       <c r="Q69" t="n">
         <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>50</v>
+        <v>377</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2012993603</t>
+          <t>1216076936</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012993603</t>
+          <t>https://m.place.naver.com/place/1216076936</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6920,34 +6920,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>하프네일</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>half7571@naver.com</t>
-        </is>
-      </c>
+          <t>루미온네일 검단신도시점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1380-7571</t>
+          <t>0507-1347-5944</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
+          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/half_nail</t>
+          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6957,7 +6953,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6977,13 +6973,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1613</v>
+        <v>43</v>
       </c>
       <c r="Q70" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="R70" t="n">
-        <v>1804</v>
+        <v>51</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6992,12 +6988,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1259862588</t>
+          <t>2012993603</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259862588</t>
+          <t>https://m.place.naver.com/place/2012993603</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7014,29 +7010,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
+          <t>하프네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dlgufl0924@naver.com</t>
+          <t>half7571@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1408-0807</t>
+          <t>0507-1380-7571</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
+          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lantienail_official/</t>
+          <t>https://www.instagram.com/half_nail</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7071,13 +7067,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>610</v>
+        <v>1613</v>
       </c>
       <c r="Q71" t="n">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="R71" t="n">
-        <v>828</v>
+        <v>1804</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7086,12 +7082,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>37922472</t>
+          <t>1259862588</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37922472</t>
+          <t>https://m.place.naver.com/place/1259862588</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7108,29 +7104,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>감성네일</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>gamseongnail@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1424-4545</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7165,13 +7161,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>449</v>
+        <v>610</v>
       </c>
       <c r="Q72" t="n">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="R72" t="n">
-        <v>614</v>
+        <v>828</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7180,12 +7176,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7202,29 +7198,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일또온나 청라점</t>
+          <t>감성네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2xmania2xj@naver.com</t>
+          <t>gamseongnail@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1338-3150</t>
+          <t>0507-1424-4545</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_tto_onna</t>
+          <t>https://www.instagram.com/gam_seongnail/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7259,13 +7255,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>247</v>
+        <v>449</v>
       </c>
       <c r="Q73" t="n">
-        <v>63</v>
+        <v>165</v>
       </c>
       <c r="R73" t="n">
-        <v>310</v>
+        <v>614</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7274,12 +7270,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1546215593</t>
+          <t>1382824710</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546215593</t>
+          <t>https://m.place.naver.com/place/1382824710</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7296,29 +7292,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일도속눈썹</t>
+          <t>네일또온나 청라점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>naildorash1@naver.com</t>
+          <t>2xmania2xj@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1395-6008</t>
+          <t>0507-1338-3150</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로 346-1 1층</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildo_lash</t>
+          <t>https://www.instagram.com/nail_tto_onna</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7344,7 +7340,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7353,13 +7349,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>404</v>
+        <v>247</v>
       </c>
       <c r="Q74" t="n">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="R74" t="n">
-        <v>693</v>
+        <v>310</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7368,12 +7364,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1958392738</t>
+          <t>1546215593</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958392738</t>
+          <t>https://m.place.naver.com/place/1546215593</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">

--- a/naver-place-crawler/results_nail/서구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서구_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>다린네일</t>
+          <t>이르미네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rodacompany@naver.com</t>
+          <t>aboutdanchuu@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1419-3567</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한중로 10 메르시타워 501호(1층 메가커피건물5층)</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/DARIN.GLOBAL</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="R2" t="n">
-        <v>224</v>
+        <v>342</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1665621156</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1665621156</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일을기억해</t>
+          <t>네일으니크</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rimo0904@naver.com</t>
+          <t>yulee410@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1491-7279</t>
+          <t>0507-1394-1471</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/remember._nails</t>
+          <t>https://pf.kakao.com/_xjfJWG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>210</v>
+        <v>433</v>
       </c>
       <c r="Q3" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="R3" t="n">
-        <v>254</v>
+        <v>521</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1811328950</t>
+          <t>1466509562</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811328950</t>
+          <t>https://m.place.naver.com/place/1466509562</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일으니크</t>
+          <t>루미온네일 검단신도시점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yulee410@naver.com</t>
+          <t>rowawoo@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1394-1471</t>
+          <t>0507-1347-5944</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티 6층 628호</t>
+          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjfJWG</t>
+          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>431</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="n">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>519</v>
+        <v>54</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1466509562</t>
+          <t>2012993603</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466509562</t>
+          <t>https://m.place.naver.com/place/2012993603</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일하고가람</t>
+          <t>포네하네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dkfzhdspdlf@naver.com</t>
+          <t>forestnh@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1468-0177</t>
+          <t>0507-1400-8523</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailharam_</t>
+          <t>https://blog.naver.com/forestnh</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>339</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="R5" t="n">
-        <v>126</v>
+        <v>455</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1958882228</t>
+          <t>1672609930</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958882228</t>
+          <t>https://m.place.naver.com/place/1672609930</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,25 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>라벨르뷰티</t>
+          <t>쏘네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>labelle0322@naver.com</t>
+          <t>choseohyun041019@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1371-4660</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
+          <t>인천광역시 서구 봉오재3로 90 2층 쏘네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/la__belle_beauty</t>
+          <t>https://www.instagram.com/_sso_shop__/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1115</v>
+        <v>835</v>
       </c>
       <c r="Q6" t="n">
-        <v>253</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>1368</v>
+        <v>846</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1968058232</t>
+          <t>1293272639</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968058232</t>
+          <t>https://m.place.naver.com/place/1293272639</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일도빛나</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sjh888347@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1302-9518</t>
+          <t>0507-1344-1735</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 551 동곡프라자 1층 107호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildo_bitna</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>477</v>
+        <v>259</v>
       </c>
       <c r="Q7" t="n">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>572</v>
+        <v>288</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1239607974</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239607974</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>인생네일 청라본점</t>
+          <t>네일하롱</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>askflclsrna@naver.com</t>
+          <t>mimmmm95_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1301-5228</t>
+          <t>0507-1438-1442</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/life_nail_salon</t>
+          <t>https://www.instagram.com/nail._.harong</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>351</v>
+        <v>536</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R8" t="n">
-        <v>362</v>
+        <v>572</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1764464663</t>
+          <t>1264211104</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764464663</t>
+          <t>https://m.place.naver.com/place/1264211104</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
+          <t>풋라인 / 발각질 무좀발톱 손톱 내성발톱</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mina20624@naver.com</t>
+          <t>footline_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1332-6316</t>
+          <t>0507-1413-5896</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 서곶로 50 3동 2층 B226호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>https://blog.naver.com/footline_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>665</v>
+        <v>93</v>
       </c>
       <c r="Q9" t="n">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="R9" t="n">
-        <v>832</v>
+        <v>133</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>1082466960</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/1082466960</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1312,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>오늘의기분 네일 청라본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>bae_tamine@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1307-8929</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>http://pf.kakao.com/_pxcsgb</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>620</v>
+        <v>354</v>
       </c>
       <c r="Q10" t="n">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="R10" t="n">
-        <v>751</v>
+        <v>431</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1747055394</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1747055394</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1406,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일희 검단신도시점</t>
+          <t>네일벨</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gosm06@naver.com</t>
+          <t>nailbelle@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1398-9916</t>
+          <t>0507-1324-7499</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
+          <t>인천광역시 서구 원창로229번길 39 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailhee_</t>
+          <t>http://pf.kakao.com/_Nmwmxb</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1454,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>344</v>
+        <v>139</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>215</v>
       </c>
       <c r="R11" t="n">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1280546741</t>
+          <t>1895861710</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280546741</t>
+          <t>https://m.place.naver.com/place/1895861710</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1504,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>달미네일</t>
+          <t>네일바연</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jinjoo8570@naver.com</t>
+          <t>yeerina@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1513,22 +1517,22 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
+          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/aWKRY9YJt</t>
+          <t>http://instagram.com/nail.by.yeon</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1553,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>204</v>
+        <v>690</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R12" t="n">
-        <v>214</v>
+        <v>715</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2000818117</t>
+          <t>1017865788</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000818117</t>
+          <t>https://m.place.naver.com/place/1017865788</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아트스타일네일</t>
+          <t>프롬쥬네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gotitkorea@naver.com</t>
+          <t>dlaalswn89@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1418-1574</t>
+          <t>0507-1327-0666</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 30 416호</t>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
+          <t>https://blog.naver.com/dlaalswn89</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1631,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>117</v>
+        <v>567</v>
       </c>
       <c r="Q13" t="n">
-        <v>296</v>
+        <v>133</v>
       </c>
       <c r="R13" t="n">
-        <v>413</v>
+        <v>700</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1976908458</t>
+          <t>1545913000</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976908458</t>
+          <t>https://m.place.naver.com/place/1545913000</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>무드온네일</t>
+          <t>어레브네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>llggggll@naver.com</t>
+          <t>anwlro9344@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1494-6716</t>
+          <t>0507-1354-5482</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moodon.nail</t>
+          <t>https://blog.naver.com/anwlro9344</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1721,7 +1725,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1741,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2044601280</t>
+          <t>1364434683</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044601280</t>
+          <t>https://m.place.naver.com/place/1364434683</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>소담뷰티 검단신도시점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>on323652@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>0507-1484-9220</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>https://www.instagram.com/sodam_beauty1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1815,7 +1819,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>567</v>
+        <v>217</v>
       </c>
       <c r="Q15" t="n">
-        <v>133</v>
+        <v>328</v>
       </c>
       <c r="R15" t="n">
-        <v>700</v>
+        <v>545</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>1342897161</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/1342897161</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>오오샵 검단점</t>
+          <t>감성네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dhaldud10@naver.com</t>
+          <t>gamseongnail@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>070-4062-0556</t>
+          <t>0507-1424-4545</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 159 1층 105호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop/</t>
+          <t>https://www.instagram.com/gam_seongnail/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1929,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>623</v>
+        <v>452</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="R16" t="n">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1739642099</t>
+          <t>1382824710</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739642099</t>
+          <t>https://m.place.naver.com/place/1382824710</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일델루나</t>
+          <t>제이언니네 청라본점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eatingzzz@naver.com</t>
+          <t>mina20624@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1358-7017</t>
+          <t>0507-1332-6316</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_delluna</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2023,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1534</v>
+        <v>666</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="R17" t="n">
-        <v>1549</v>
+        <v>833</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1852644091</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852644091</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>루안네일 토탈뷰티 검단점</t>
+          <t>지혜로운 네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>luannail@naver.com</t>
+          <t>liz_kang@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1349-7727</t>
+          <t>0507-1482-5955</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 단봉로 97-7 1층 112호</t>
+          <t>인천광역시 서구 이음1로 383 세중시그니처 310호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://http//pf.kakao.com/_vALxgG</t>
+          <t>https://www.instagram.com/jihyerowoon.nail/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2117,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>742</v>
+        <v>561</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="R18" t="n">
-        <v>745</v>
+        <v>580</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1840082670</t>
+          <t>1492433716</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840082670</t>
+          <t>https://m.place.naver.com/place/1492433716</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2154,25 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>카밀라네일 검단신도시점</t>
+          <t>네일달다 청라점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ojolfkj@naver.com</t>
+          <t>haru_log_in@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1325-3255</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
+          <t>http://instagram.com/naildalda_</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>759</v>
+        <v>626</v>
       </c>
       <c r="Q19" t="n">
-        <v>369</v>
+        <v>241</v>
       </c>
       <c r="R19" t="n">
-        <v>1128</v>
+        <v>867</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1490697723</t>
+          <t>1040857451</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490697723</t>
+          <t>https://m.place.naver.com/place/1040857451</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>루씨르네일 물어뜯는 손톱연장 노가시스템</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lucirnail_@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1369-3734</t>
+          <t>0507-1346-5358</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 390 1층 107호</t>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lucirnail_</t>
+          <t>https://www.instagram.com/nail.grimmy</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2281,7 +2289,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2301,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="Q20" t="n">
-        <v>148</v>
+        <v>54</v>
       </c>
       <c r="R20" t="n">
-        <v>225</v>
+        <v>404</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1871859211</t>
+          <t>1125220368</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1871859211</t>
+          <t>https://m.place.naver.com/place/1125220368</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2338,30 +2346,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일바연</t>
+          <t>블링뷰네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>yeerina@naver.com</t>
+          <t>bv_nail@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1350-9502</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 474 뷰비스타운 3층 303호 네일바연</t>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.by.yeon</t>
+          <t>http://pf.kakao.com/_RqUxcG</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2382,7 +2394,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2391,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>688</v>
+        <v>118</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="R21" t="n">
-        <v>713</v>
+        <v>271</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1017865788</t>
+          <t>1259415075</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017865788</t>
+          <t>https://m.place.naver.com/place/1259415075</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2440,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일위드유 문제성발톱 속눈썹</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nail_with_yoo@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1344-1735</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_with_yoo</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2465,7 +2477,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2481,17 +2493,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>259</v>
+        <v>907</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>380</v>
       </c>
       <c r="R22" t="n">
-        <v>288</v>
+        <v>1287</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1776289071</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776289071</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2522,30 +2534,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일에딧</t>
+          <t>네일희 검단신도시점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>byddooroo@naver.com</t>
+          <t>gosm06@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1398-9916</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
+          <t>인천광역시 서구 이음5로 30 연세프라자9 410호 네일희</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dZxhxcn</t>
+          <t>https://www.instagram.com/_nailhee_</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2566,7 +2582,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2575,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>801</v>
+        <v>345</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="R23" t="n">
-        <v>807</v>
+        <v>360</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2590,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2041818773</t>
+          <t>1280546741</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041818773</t>
+          <t>https://m.place.naver.com/place/1280546741</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2612,29 +2628,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>네일디핀</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mobi04@naver.com</t>
+          <t>sina1310@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1398-8291</t>
+          <t>0507-1476-4029</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>https://www.instagram.com/naildeepin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2669,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>573</v>
+        <v>89</v>
       </c>
       <c r="Q24" t="n">
-        <v>846</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1419</v>
+        <v>96</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>2047454568</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/2047454568</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2706,29 +2722,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1248네일</t>
+          <t>네일하고가람</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1248nail@naver.com</t>
+          <t>fromantic@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1479-8978</t>
+          <t>0507-1468-0177</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+          <t>인천광역시 서구 고산후로 222 푸리마더타워 211호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1248_nail</t>
+          <t>https://www.instagram.com/nailharam_</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2763,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>457</v>
+        <v>106</v>
       </c>
       <c r="Q25" t="n">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="R25" t="n">
-        <v>724</v>
+        <v>126</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2778,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1537239618</t>
+          <t>1958882228</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537239618</t>
+          <t>https://m.place.naver.com/place/1958882228</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2800,29 +2816,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>모하카 네일</t>
+          <t>소요뷰티</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>khss11550@naver.com</t>
+          <t>raindrop3113@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1376-7909</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 12 다승프라자 2차 602호</t>
+          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmohaka</t>
+          <t>https://www.instagram.com/soyo._.beauty</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2857,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>169</v>
+        <v>578</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>202</v>
+        <v>583</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2884,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1979256613</t>
+          <t>1142806255</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979256613</t>
+          <t>https://m.place.naver.com/place/1142806255</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2894,25 +2906,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>도르네일</t>
+          <t>악어네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bnm4818@naver.com</t>
+          <t>bestone4848@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1325-3157</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/hCmFKNexK</t>
+          <t>http://pf.kakao.com/_qxjdtG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2922,7 +2938,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2938,7 +2954,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2947,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>728</v>
+        <v>309</v>
       </c>
       <c r="Q27" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>782</v>
+        <v>319</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,17 +2978,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1001824596</t>
+          <t>1369177883</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001824596</t>
+          <t>https://m.place.naver.com/place/1369177883</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2984,29 +3000,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>오늘도네일도</t>
+          <t>네일인유</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nail_oneul@naver.com</t>
+          <t>bonheur0118@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1449-7506</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_oneul</t>
+          <t>https://www.instagram.com/nail_inyou</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3021,7 +3033,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3041,13 +3053,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>816</v>
+        <v>1190</v>
       </c>
       <c r="Q28" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="R28" t="n">
-        <v>858</v>
+        <v>1205</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,17 +3068,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1810678383</t>
+          <t>1117254073</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810678383</t>
+          <t>https://m.place.naver.com/place/1117254073</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3078,34 +3090,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>악어네일&amp;속눈썹</t>
+          <t>루안네일 토탈뷰티 검단점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bestone4848@naver.com</t>
+          <t>luannail@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1325-3157</t>
+          <t>0507-1349-7727</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 45 루원 린스트라우스 앨리스빌 상가 1층 1097호</t>
+          <t>인천광역시 서구 단봉로 97-7 1층 112호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qxjdtG</t>
+          <t>https://http//pf.kakao.com/_vALxgG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3135,13 +3147,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>308</v>
+        <v>745</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>318</v>
+        <v>748</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3162,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1369177883</t>
+          <t>1840082670</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369177883</t>
+          <t>https://m.place.naver.com/place/1840082670</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3172,29 +3184,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일이음 검단신도시점</t>
+          <t>1248네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>slovejy@naver.com</t>
+          <t>1248nail@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1373-3055</t>
+          <t>0507-1479-8978</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailieum</t>
+          <t>https://www.instagram.com/1248_nail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3229,13 +3241,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1324</v>
+        <v>457</v>
       </c>
       <c r="Q30" t="n">
-        <v>72</v>
+        <v>267</v>
       </c>
       <c r="R30" t="n">
-        <v>1396</v>
+        <v>724</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,17 +3256,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1729889261</t>
+          <t>1537239618</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729889261</t>
+          <t>https://m.place.naver.com/place/1537239618</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3266,29 +3278,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>어레브네일</t>
+          <t>카밀라네일 검단신도시점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>anwlro9344@naver.com</t>
+          <t>ojolfkj@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1354-5482</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
+          <t>인천광역시 서구 이음대로 384 서영아너시티 플러스 227, 228호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anwlro9344</t>
+          <t>https://www.instagram.com/camila__nail_?igsh=MWVteno3MnNqNHd0eA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3303,7 +3311,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3323,13 +3331,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>70</v>
+        <v>759</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>375</v>
       </c>
       <c r="R31" t="n">
-        <v>75</v>
+        <v>1134</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3346,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1364434683</t>
+          <t>1490697723</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364434683</t>
+          <t>https://m.place.naver.com/place/1490697723</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3360,34 +3368,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>이루아네일</t>
+          <t>네일무디크</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>nec1153@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1375-3428</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>https://www.instagram.com/nail_moodique</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3417,13 +3425,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="R32" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3440,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1811715033</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1811715033</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3454,34 +3462,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>신스티니네일</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jin70826@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1399-4665</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_tkuSxj</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3502,7 +3510,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3511,13 +3519,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1137</v>
+        <v>610</v>
       </c>
       <c r="Q33" t="n">
-        <v>845</v>
+        <v>218</v>
       </c>
       <c r="R33" t="n">
-        <v>1982</v>
+        <v>828</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3534,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1503407402</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1503407402</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3548,34 +3556,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>이르미네일</t>
+          <t>루비네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>aboutdanchuu@naver.com</t>
+          <t>ruby1004_mj@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1391-3129</t>
+          <t>0507-1486-3019</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ezxgrG</t>
+          <t>https://www.instagram.com/rubynail3006</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3596,7 +3604,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3605,13 +3613,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="Q34" t="n">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="R34" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,17 +3628,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1596414337</t>
+          <t>1233475580</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596414337</t>
+          <t>https://m.place.naver.com/place/1233475580</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3642,29 +3650,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일무우 인천검단점</t>
+          <t>아이퀸네일 청라점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>n_mou@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1382-9824</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/n_mou</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3679,7 +3687,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3699,13 +3707,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>287</v>
       </c>
       <c r="R35" t="n">
-        <v>341</v>
+        <v>601</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,17 +3722,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1965956470</t>
+          <t>1330577008</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965956470</t>
+          <t>https://m.place.naver.com/place/1330577008</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3736,29 +3744,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일하롱</t>
+          <t>네일,사계절</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mimmmm95_@naver.com</t>
+          <t>siryyam@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1438-1442</t>
+          <t>0507-1360-4822</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.harong</t>
+          <t>https://www.instagram.com/nail_4season</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3793,13 +3801,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>536</v>
+        <v>369</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="R36" t="n">
-        <v>572</v>
+        <v>377</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,17 +3816,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1264211104</t>
+          <t>1216076936</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264211104</t>
+          <t>https://m.place.naver.com/place/1216076936</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3830,39 +3838,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>소담뷰티 검단신도시점</t>
+          <t>달미네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>on323652@naver.com</t>
+          <t>jinjoo8570@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0507-1484-9220</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 66 1동 3층 307호</t>
+          <t>인천광역시 서구 봉오재3로 124 루원시티 디오스텔 1층 111호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sodam_beauty1</t>
+          <t>https://toss.place/_lb/aWKRY9YJt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3887,13 +3891,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="Q37" t="n">
-        <v>327</v>
+        <v>10</v>
       </c>
       <c r="R37" t="n">
-        <v>546</v>
+        <v>217</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3906,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1342897161</t>
+          <t>2000818117</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342897161</t>
+          <t>https://m.place.naver.com/place/2000818117</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3924,29 +3928,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>바리에라네일</t>
+          <t>오오샵 가좌점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rosekim1102@naver.com</t>
+          <t>dodofamily_mam@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1390-9307</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 8 409호</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/varier_la_nail</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3981,13 +3985,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>172</v>
+        <v>406</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R38" t="n">
-        <v>211</v>
+        <v>446</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +4000,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2090298265</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090298265</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4018,34 +4022,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일갱 인천검단점</t>
+          <t>섬세하나네일 청라본점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nailgang_@naver.com</t>
+          <t>sumsehana@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1353-4100</t>
+          <t>0507-1481-0788</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bJxdCG</t>
+          <t>https://blog.naver.com/sumsehana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4055,7 +4059,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4066,7 +4070,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4075,13 +4079,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1700</v>
+        <v>621</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="R39" t="n">
-        <v>1731</v>
+        <v>752</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4094,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1098311831</t>
+          <t>1251340543</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098311831</t>
+          <t>https://m.place.naver.com/place/1251340543</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4112,25 +4116,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일인유</t>
+          <t>바리에라네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bonheur0118@naver.com</t>
+          <t>rosekim1102@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1390-9307</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로685번길 5 당하3차풍림아파트 후문(B동) 상가 2층</t>
+          <t>인천광역시 서구 바리미로5번길 8 골든스퀘어, 409호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_inyou</t>
+          <t>https://www.instagram.com/varier_la_nail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4165,13 +4173,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1186</v>
+        <v>173</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="R40" t="n">
-        <v>1201</v>
+        <v>213</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4188,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1117254073</t>
+          <t>2090298265</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117254073</t>
+          <t>https://m.place.naver.com/place/2090298265</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4202,29 +4210,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>온다네일룸</t>
+          <t>오오샵 서구청점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dl7246@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1369-7246</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 179 3층</t>
+          <t>인천광역시 서구 심곡로 44-1 108호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onda_nail_room/</t>
+          <t>https://www.instagram.com/55shop_simgock</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4259,13 +4263,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>755</v>
+        <v>137</v>
       </c>
       <c r="Q41" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="R41" t="n">
-        <v>801</v>
+        <v>149</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,17 +4278,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1656364709</t>
+          <t>1488480006</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656364709</t>
+          <t>https://m.place.naver.com/place/1488480006</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4296,25 +4300,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>오오샵 서구청점</t>
+          <t>해온네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>cocory_snb@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1368-2279</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 심곡로 44-1 108호</t>
+          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55shop_simgock</t>
+          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4345,17 +4353,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R42" t="n">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,17 +4372,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1488480006</t>
+          <t>2095874863</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488480006</t>
+          <t>https://m.place.naver.com/place/2095874863</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4386,29 +4394,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일드벨라 인천검단점</t>
+          <t>무드온네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>naildebella@naver.com</t>
+          <t>llggggll@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1356-3442</t>
+          <t>0507-1494-6716</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 384 307호</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층, 205호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildebella</t>
+          <t>https://www.instagram.com/moodon.nail</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4423,7 +4431,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4443,13 +4451,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>264</v>
+        <v>57</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="R43" t="n">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,17 +4466,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1219318994</t>
+          <t>2044601280</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1219318994</t>
+          <t>https://m.place.naver.com/place/2044601280</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4480,29 +4488,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>네일또온나 청라점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>2xmania2xj@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1346-5358</t>
+          <t>0507-1338-3150</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.grimmy</t>
+          <t>https://www.instagram.com/nail_tto_onna</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4537,13 +4545,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>349</v>
+        <v>247</v>
       </c>
       <c r="Q44" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="R44" t="n">
-        <v>403</v>
+        <v>310</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,17 +4560,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1125220368</t>
+          <t>1546215593</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125220368</t>
+          <t>https://m.place.naver.com/place/1546215593</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4574,34 +4582,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>블링뷰네일</t>
+          <t>아트스타일네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bv_nail@naver.com</t>
+          <t>bi1142@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1350-9502</t>
+          <t>0507-1418-1574</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+          <t>인천광역시 서구 염곡로464번길 30 416호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RqUxcG</t>
+          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4622,7 +4630,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4631,13 +4639,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q45" t="n">
-        <v>153</v>
+        <v>296</v>
       </c>
       <c r="R45" t="n">
-        <v>271</v>
+        <v>413</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,17 +4654,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1259415075</t>
+          <t>1976908458</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259415075</t>
+          <t>https://m.place.naver.com/place/1976908458</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4668,29 +4676,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라나뷰티 청라본점</t>
+          <t>와우뷰티 청라점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1392-1325</t>
+          <t>0507-1323-1043</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_rananail</t>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4716,7 +4724,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4725,13 +4733,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>460</v>
+        <v>92</v>
       </c>
       <c r="Q46" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="R46" t="n">
-        <v>485</v>
+        <v>141</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4748,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1071013615</t>
+          <t>1012993987</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071013615</t>
+          <t>https://m.place.naver.com/place/1012993987</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4762,29 +4770,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>손끝한올네일</t>
+          <t>네일델루나</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>foiri@naver.com</t>
+          <t>eatingzzz@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1392-5639</t>
+          <t>0507-1358-7017</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로 17 2층 203호</t>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
+          <t>http://instagram.com/nail_delluna</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4819,13 +4827,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>77</v>
+        <v>1536</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R47" t="n">
-        <v>95</v>
+        <v>1551</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,17 +4842,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2013624857</t>
+          <t>1852644091</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013624857</t>
+          <t>https://m.place.naver.com/place/1852644091</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4856,34 +4864,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>루비네일</t>
+          <t>네일다름 인천검단점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ruby1004_mj@naver.com</t>
+          <t>naildareum_@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1486-3019</t>
+          <t>0507-1431-4140</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한들로 73 로열파크씨티 2단지 상가6 207호</t>
+          <t>인천광역시 서구 이음5로 20 연세프라자 8차 309호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rubynail3006</t>
+          <t>http://pf.kakao.com/_CIgvC</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4904,7 +4912,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4913,13 +4921,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>280</v>
+        <v>430</v>
       </c>
       <c r="Q48" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="R48" t="n">
-        <v>343</v>
+        <v>532</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,17 +4936,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1233475580</t>
+          <t>1735874545</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233475580</t>
+          <t>https://m.place.naver.com/place/1735874545</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4950,29 +4958,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일드림</t>
+          <t>라벨르뷰티</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>shsally0122@naver.com</t>
+          <t>labelle0322@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1335-1809</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
+          <t>인천광역시 서구 이음대로 378 로뎀타워 4층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://instagram.com/naild_lim</t>
+          <t>https://www.instagram.com/la__belle_beauty</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5007,13 +5011,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>356</v>
+        <v>1115</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>253</v>
       </c>
       <c r="R49" t="n">
-        <v>364</v>
+        <v>1368</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,17 +5026,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1192065742</t>
+          <t>1968058232</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192065742</t>
+          <t>https://m.place.naver.com/place/1968058232</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5044,29 +5048,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>오오샵 검단점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>dhaldud10@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>070-4062-0556</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 완정로 159 1층 105호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>https://www.instagram.com/55_allinone_shop/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5081,7 +5085,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5101,13 +5105,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>337</v>
+        <v>627</v>
       </c>
       <c r="Q50" t="n">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="R50" t="n">
-        <v>453</v>
+        <v>652</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,17 +5120,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1739642099</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1739642099</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5138,34 +5142,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일디핀</t>
+          <t>신스티니네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sina1310@naver.com</t>
+          <t>jin70826@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1476-4029</t>
+          <t>0507-1399-4665</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 837 당하빌딩 3층 네일디핀</t>
+          <t>인천광역시 서구 이음5로 62 . 5층 506호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildeepin</t>
+          <t>http://pf.kakao.com/_tkuSxj</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5186,7 +5190,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5195,13 +5199,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>89</v>
+        <v>1138</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>845</v>
       </c>
       <c r="R51" t="n">
-        <v>96</v>
+        <v>1983</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,17 +5214,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2047454568</t>
+          <t>1503407402</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047454568</t>
+          <t>https://m.place.naver.com/place/1503407402</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5232,29 +5236,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>뉴아네일</t>
+          <t>단감네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kikiki_k@naver.com</t>
+          <t>aayoon7@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1336-2796</t>
+          <t>0507-1374-8432</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 418 101호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newa_nail25</t>
+          <t>https://www.instagram.com/dangam_nail/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5289,13 +5293,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>89</v>
+        <v>207</v>
       </c>
       <c r="Q52" t="n">
-        <v>128</v>
+        <v>337</v>
       </c>
       <c r="R52" t="n">
-        <v>217</v>
+        <v>544</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,17 +5308,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1799034051</t>
+          <t>1985862694</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799034051</t>
+          <t>https://m.place.naver.com/place/1985862694</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5326,25 +5330,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>소요뷰티</t>
+          <t>오늘도네일도</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>raindrop3113@naver.com</t>
+          <t>nail_oneul@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1449-7506</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미 2차, 7층 733호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soyo._.beauty</t>
+          <t>https://blog.naver.com/nail_oneul</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5359,7 +5367,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5379,13 +5387,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>577</v>
+        <v>818</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="R53" t="n">
-        <v>582</v>
+        <v>860</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,17 +5402,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1142806255</t>
+          <t>1810678383</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142806255</t>
+          <t>https://m.place.naver.com/place/1810678383</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5416,34 +5424,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일벨</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nailbelle@naver.com</t>
+          <t>mobi04@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1324-7499</t>
+          <t>0507-1398-8291</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원창로229번길 39 1층</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Nmwmxb</t>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5464,7 +5472,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5473,13 +5481,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>139</v>
+        <v>573</v>
       </c>
       <c r="Q54" t="n">
-        <v>215</v>
+        <v>852</v>
       </c>
       <c r="R54" t="n">
-        <v>354</v>
+        <v>1425</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,17 +5496,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1895861710</t>
+          <t>1090442730</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895861710</t>
+          <t>https://m.place.naver.com/place/1090442730</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5510,34 +5518,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>풋라인 / 발각질 무좀발톱 손톱 내성발톱</t>
+          <t>네일갱 인천검단점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>footline_@naver.com</t>
+          <t>nailgang_@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1413-5896</t>
+          <t>0507-1353-4100</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 50 3동 2층 B226호</t>
+          <t>인천광역시 서구 청마로51번안길 14 2층 네일갱</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/footline_</t>
+          <t>http://pf.kakao.com/_bJxdCG</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5547,7 +5555,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5558,22 +5566,22 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>93</v>
+        <v>1700</v>
       </c>
       <c r="Q55" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="R55" t="n">
-        <v>133</v>
+        <v>1731</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,17 +5590,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1082466960</t>
+          <t>1098311831</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1082466960</t>
+          <t>https://m.place.naver.com/place/1098311831</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5604,29 +5612,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일달다 청라점</t>
+          <t>다린네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>haru_log_in@naver.com</t>
+          <t>traveldolphin@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1325-3255</t>
+          <t>0507-1419-3567</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+          <t>인천광역시 서구 한중로 10 메르시타워 501호(1층 메가커피건물5층)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildalda_</t>
+          <t>https://www.instagram.com/DARIN.GLOBAL</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5661,13 +5669,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>622</v>
+        <v>212</v>
       </c>
       <c r="Q56" t="n">
-        <v>240</v>
+        <v>12</v>
       </c>
       <c r="R56" t="n">
-        <v>862</v>
+        <v>224</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,17 +5684,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1040857451</t>
+          <t>1665621156</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040857451</t>
+          <t>https://m.place.naver.com/place/1665621156</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5698,29 +5706,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>레푸스 청라점</t>
+          <t>미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>dldeoqkr@naver.com</t>
+          <t>mielnailbrow@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1337-0812</t>
+          <t>0507-1355-4026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYKKOFJe</t>
+          <t>https://www.instagram.com/mielnailbrow_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5746,7 +5754,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5755,13 +5763,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>301</v>
+        <v>731</v>
       </c>
       <c r="Q57" t="n">
-        <v>68</v>
+        <v>402</v>
       </c>
       <c r="R57" t="n">
-        <v>369</v>
+        <v>1133</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5770,17 +5778,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1742485791</t>
+          <t>409746804</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742485791</t>
+          <t>https://m.place.naver.com/place/409746804</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5792,34 +5800,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
+          <t>모하카 네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bae_tamine@naver.com</t>
+          <t>khss11550@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1376-7909</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 바리미로5번길 12 다승프라자 2차 602호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>https://www.instagram.com/nailmohaka</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5840,7 +5848,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5849,13 +5857,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>353</v>
+        <v>171</v>
       </c>
       <c r="Q58" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="R58" t="n">
-        <v>430</v>
+        <v>204</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5864,17 +5872,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>1979256613</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/1979256613</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5886,29 +5894,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>미엘네일브로우 인천가정점</t>
+          <t>라나뷰티 청라본점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mielnailbrow@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1355-4026</t>
+          <t>0507-1392-1325</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 210호 미엘네일브로우 인천가정점</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mielnailbrow_</t>
+          <t>https://www.instagram.com/_rananail</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5934,7 +5942,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5943,13 +5951,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>731</v>
+        <v>461</v>
       </c>
       <c r="Q59" t="n">
-        <v>401</v>
+        <v>25</v>
       </c>
       <c r="R59" t="n">
-        <v>1132</v>
+        <v>486</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5958,17 +5966,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>409746804</t>
+          <t>1071013615</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/409746804</t>
+          <t>https://m.place.naver.com/place/1071013615</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5980,29 +5988,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>블링루원뷰티</t>
+          <t>네일이음 검단신도시점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ball_11058@naver.com</t>
+          <t>slovejy@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1462-3543</t>
+          <t>0507-1373-3055</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
+          <t>인천광역시 서구 이음5로 39 우미린더시그니처 상가1동 105호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailieum</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6012,7 +6020,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6033,17 +6041,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>228</v>
+        <v>1329</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="R60" t="n">
-        <v>237</v>
+        <v>1401</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6052,17 +6060,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1323823289</t>
+          <t>1729889261</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323823289</t>
+          <t>https://m.place.naver.com/place/1729889261</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6074,34 +6082,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에스영이네일</t>
+          <t>젤로미네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>s02nail@naver.com</t>
+          <t>nailjellomi@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1322-9488</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
+          <t>인천광역시 서구 검단로 480 3층 305호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JAxdFs</t>
+          <t>https://www.instagram.com/nail._.jellomi</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6122,7 +6126,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6131,13 +6135,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>428</v>
+        <v>93</v>
       </c>
       <c r="Q61" t="n">
-        <v>188</v>
+        <v>51</v>
       </c>
       <c r="R61" t="n">
-        <v>616</v>
+        <v>144</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6146,17 +6150,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1726483094</t>
+          <t>2051638884</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726483094</t>
+          <t>https://m.place.naver.com/place/2051638884</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6168,29 +6172,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일무디크</t>
+          <t>뉴아네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>kikiki_k@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1375-3428</t>
+          <t>0507-1336-2796</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+          <t>인천광역시 서구 승학로 418 101호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_moodique</t>
+          <t>https://www.instagram.com/newa_nail25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6225,13 +6229,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="R62" t="n">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6240,17 +6244,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1811715033</t>
+          <t>1799034051</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811715033</t>
+          <t>https://m.place.naver.com/place/1799034051</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6262,29 +6266,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>단감네일</t>
+          <t>네일무우 인천검단점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sytf170@naver.com</t>
+          <t>n_mou@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1374-8432</t>
+          <t>0507-1382-9824</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+          <t>인천광역시 서구 이음4로 6 kr법조타워 6층 613호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dangam_nail/</t>
+          <t>https://blog.naver.com/n_mou</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6299,7 +6303,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6319,13 +6323,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>207</v>
+        <v>328</v>
       </c>
       <c r="Q63" t="n">
-        <v>337</v>
+        <v>14</v>
       </c>
       <c r="R63" t="n">
-        <v>544</v>
+        <v>342</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6334,17 +6338,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1985862694</t>
+          <t>1965956470</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985862694</t>
+          <t>https://m.place.naver.com/place/1965956470</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6356,29 +6360,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
+          <t>블링루원뷰티</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gamejaki@naver.com</t>
+          <t>ball_11058@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1462-3543</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6388,7 +6392,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6409,17 +6413,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>314</v>
+        <v>230</v>
       </c>
       <c r="Q64" t="n">
-        <v>273</v>
+        <v>9</v>
       </c>
       <c r="R64" t="n">
-        <v>587</v>
+        <v>239</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6428,17 +6432,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>1323823289</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/1323823289</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6450,29 +6454,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>레푸스검단점&amp;로브</t>
+          <t>온다네일룸</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>refussgumdan@naver.com</t>
+          <t>dl7246@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1345-7844</t>
+          <t>0507-1369-7246</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
+          <t>인천광역시 서구 완정로 179 3층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_gumdan</t>
+          <t>https://www.instagram.com/onda_nail_room/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6507,13 +6511,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>513</v>
+        <v>757</v>
       </c>
       <c r="Q65" t="n">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="R65" t="n">
-        <v>663</v>
+        <v>803</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6522,17 +6526,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1967477084</t>
+          <t>1656364709</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967477084</t>
+          <t>https://m.place.naver.com/place/1656364709</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6544,29 +6548,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>네일드벨라 인천검단점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>naildebella@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1309-5041</t>
+          <t>0507-1356-3442</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+          <t>인천광역시 서구 이음대로 384 307호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+          <t>https://blog.naver.com/naildebella</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6581,7 +6585,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6601,13 +6605,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="R66" t="n">
-        <v>221</v>
+        <v>300</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6616,17 +6620,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1024146721</t>
+          <t>1219318994</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024146721</t>
+          <t>https://m.place.naver.com/place/1219318994</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6638,29 +6642,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>와우뷰티 청라점</t>
+          <t>손끝한올네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>foiri@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1323-1043</t>
+          <t>0507-1392-5639</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+          <t>인천광역시 서구 바리미로 17 2층 203호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_hanol?igsh=MWpqaDVieHRnZTF3Ng==</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6695,13 +6699,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="Q67" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="R67" t="n">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6710,17 +6714,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1012993987</t>
+          <t>2013624857</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012993987</t>
+          <t>https://m.place.naver.com/place/2013624857</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6732,44 +6736,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+          <t>도르네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01192291122@naver.com</t>
+          <t>bnm4818@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1338-0068</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/01192291122</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6785,17 +6785,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>907</v>
+        <v>733</v>
       </c>
       <c r="Q68" t="n">
-        <v>380</v>
+        <v>54</v>
       </c>
       <c r="R68" t="n">
-        <v>1287</v>
+        <v>787</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6804,17 +6804,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1868333219</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868333219</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6826,29 +6826,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일,사계절</t>
+          <t>인생네일 청라본점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>siryyam@naver.com</t>
+          <t>askflclsrna@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1360-4822</t>
+          <t>0507-1301-5228</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 24 쓰리엠 타워 204호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_4season</t>
+          <t>https://www.instagram.com/life_nail_salon</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6883,13 +6883,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R69" t="n">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6898,17 +6898,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1216076936</t>
+          <t>1764464663</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216076936</t>
+          <t>https://m.place.naver.com/place/1764464663</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6920,30 +6920,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>루미온네일 검단신도시점</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>네일에딧</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>byddooroo@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1347-5944</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 동화시로 112 1층 108-2호</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumion_nail5944?igsh=MWQ2dDEwYXRjNm82Zg==</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6964,7 +6964,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6973,13 +6973,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>43</v>
+        <v>806</v>
       </c>
       <c r="Q70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R70" t="n">
-        <v>51</v>
+        <v>812</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6988,17 +6988,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2012993603</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012993603</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7010,29 +7010,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>하프네일</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>half7571@naver.com</t>
+          <t>haery_kim@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1380-7571</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/half_nail</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7067,13 +7067,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1613</v>
+        <v>214</v>
       </c>
       <c r="Q71" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>1804</v>
+        <v>222</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7082,17 +7082,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1259862588</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259862588</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7104,29 +7104,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
+          <t>레푸스 청라점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>dlgufl0924@naver.com</t>
+          <t>dldeoqkr@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1408-0807</t>
+          <t>0507-1337-0812</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lantienail_official/</t>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7152,7 +7152,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>610</v>
+        <v>303</v>
       </c>
       <c r="Q72" t="n">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="R72" t="n">
-        <v>828</v>
+        <v>371</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,17 +7176,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>37922472</t>
+          <t>1742485791</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37922472</t>
+          <t>https://m.place.naver.com/place/1742485791</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7198,29 +7198,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>감성네일</t>
+          <t>네일드림</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>gamseongnail@naver.com</t>
+          <t>shsally0122@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1424-4545</t>
+          <t>0507-1335-1809</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>http://instagram.com/naild_lim</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7255,13 +7255,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>449</v>
+        <v>356</v>
       </c>
       <c r="Q73" t="n">
-        <v>165</v>
+        <v>8</v>
       </c>
       <c r="R73" t="n">
-        <v>614</v>
+        <v>364</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7270,17 +7270,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>1192065742</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/1192065742</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7292,29 +7292,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일또온나 청라점</t>
+          <t>하프네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2xmania2xj@naver.com</t>
+          <t>half7571@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1338-3150</t>
+          <t>0507-1380-7571</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+          <t>인천광역시 서구 검단로 480 리치웰프라자 6층 하프네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_tto_onna</t>
+          <t>https://www.instagram.com/half_nail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>247</v>
+        <v>1615</v>
       </c>
       <c r="Q74" t="n">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="R74" t="n">
-        <v>310</v>
+        <v>1806</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7364,17 +7364,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1546215593</t>
+          <t>1259862588</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546215593</t>
+          <t>https://m.place.naver.com/place/1259862588</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7386,25 +7386,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>젤로미네일</t>
+          <t>레푸스검단점&amp;로브</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>nailjellomi@naver.com</t>
+          <t>refussgumdan@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1345-7844</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 3층 305호</t>
+          <t>인천광역시 서구 이음1로 389 A플러스타워 304호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.jellomi</t>
+          <t>https://www.instagram.com/refuss_gumdan</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7439,13 +7443,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>91</v>
+        <v>513</v>
       </c>
       <c r="Q75" t="n">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="R75" t="n">
-        <v>140</v>
+        <v>663</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7454,17 +7458,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2051638884</t>
+          <t>1967477084</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051638884</t>
+          <t>https://m.place.naver.com/place/1967477084</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7476,29 +7480,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>해온네일</t>
+          <t>네일도속눈썹</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>cocory_snb@naver.com</t>
+          <t>naildorash1@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1368-2279</t>
+          <t>0507-1395-6008</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로 966 코벤트워크상가 2층 239호</t>
+          <t>인천광역시 서구 염곡로 346-1 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://qr.kakao.com/talk/.euhWl7bfDJKWIPTCWFy_aqnpxM-</t>
+          <t>http://instagram.com/naildo_lash</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7524,22 +7528,22 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>52</v>
+        <v>405</v>
       </c>
       <c r="Q76" t="n">
-        <v>19</v>
+        <v>289</v>
       </c>
       <c r="R76" t="n">
-        <v>71</v>
+        <v>694</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7548,17 +7552,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2095874863</t>
+          <t>1958392738</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095874863</t>
+          <t>https://m.place.naver.com/place/1958392738</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
